--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="55">
   <si>
     <t>process_hash</t>
   </si>
@@ -43,9 +43,42 @@
     <t>Test_Merchant</t>
   </si>
   <si>
+    <t>Test3</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>eee</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>Custom_Regulation</t>
+  </si>
+  <si>
+    <t>tesr</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>t</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
   </si>
   <si>
@@ -101,6 +134,54 @@
   </si>
   <si>
     <t>Staff supporting merchant accounts must receive adequate and up-to-date compliance training that is sufficient to enable them to perform their duties competently.</t>
+  </si>
+  <si>
+    <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.
+The identity verification process must incl</t>
+  </si>
+  <si>
+    <t>7	All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.
+8	The identity verification process must i</t>
+  </si>
+  <si>
+    <t>7	All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. its important for all payment processes. 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7	All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. its important for all payment processes.
+</t>
+  </si>
+  <si>
+    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
+  </si>
+  <si>
+    <t>8 The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business.</t>
+  </si>
+  <si>
+    <t>9 Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list.</t>
+  </si>
+  <si>
+    <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk.</t>
+  </si>
+  <si>
+    <t>11 Verification records shall be retained for a minimum period of seven years from the date of merchant account closure.</t>
+  </si>
+  <si>
+    <t>12 This chapter outlines the obligations of payment service providers with respect to consumer data collected during payment processing.</t>
+  </si>
+  <si>
+    <t>13 Payment service providers shall implement adequate technical and organizational safeguards to protect consumer data against unauthorized access, disclosure, or destruction.</t>
+  </si>
+  <si>
+    <t>7 All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. obligation</t>
+  </si>
+  <si>
+    <t>8 The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business. obligation</t>
+  </si>
+  <si>
+    <t>9 Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list. prohibition</t>
+  </si>
+  <si>
+    <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk. obligation</t>
   </si>
 </sst>
 </file>
@@ -432,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -466,7 +547,7 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -486,7 +567,7 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -506,7 +587,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -526,7 +607,7 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -546,7 +627,7 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -566,7 +647,7 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -586,7 +667,7 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -606,7 +687,7 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -626,7 +707,7 @@
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -646,7 +727,7 @@
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -666,7 +747,7 @@
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -686,7 +767,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -706,7 +787,7 @@
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -726,7 +807,7 @@
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -746,7 +827,7 @@
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -766,7 +847,7 @@
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -786,7 +867,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -806,7 +887,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -826,7 +907,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -842,16 +923,356 @@
       <c r="B21" t="s">
         <v>8</v>
       </c>
-      <c r="C21" t="s">
-        <v>9</v>
+      <c r="C21">
+        <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
       </c>
       <c r="F21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22">
+        <v>0.6777</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23">
+        <v>0.6778999999999999</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24">
+        <v>0.6841</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25">
+        <v>0.6841</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26">
+        <v>0.6841</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27">
+        <v>0.6841</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28">
+        <v>0.5894</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29">
+        <v>0.6067</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30">
+        <v>0.6036</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+      <c r="D31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31">
+        <v>0.6428</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32">
+        <v>5</v>
+      </c>
+      <c r="D32" t="s">
+        <v>48</v>
+      </c>
+      <c r="E32">
+        <v>0.4052</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33">
+        <v>0.625</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34">
+        <v>0.6039</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35">
+        <v>0.6194</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
+        <v>18</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36">
+        <v>0.6367</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37">
+        <v>0.6216</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38">
+        <v>0.6395999999999999</v>
+      </c>
+      <c r="F38" t="b">
         <v>1</v>
       </c>
     </row>

--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="80">
   <si>
     <t>process_hash</t>
   </si>
@@ -37,6 +37,9 @@
     <t>371de16080fffdbb</t>
   </si>
   <si>
+    <t>2a605ee07a180f75</t>
+  </si>
+  <si>
     <t>synthetic-compliance-rules-#1</t>
   </si>
   <si>
@@ -67,6 +70,15 @@
     <t>t</t>
   </si>
   <si>
+    <t>claude-synthetic-short</t>
+  </si>
+  <si>
+    <t>test3</t>
+  </si>
+  <si>
+    <t>sai_internal_hiring_process</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -77,6 +89,24 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
@@ -182,6 +212,57 @@
   </si>
   <si>
     <t>10 Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk. obligation</t>
+  </si>
+  <si>
+    <t>7All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services. 8The identity verification process must inc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk. 9Payment service </t>
+  </si>
+  <si>
+    <t>22If a complaint cannot be resolved within the prescribed timeframe, the provider shall escalate the matter to the Consumer Mediation Office and inform the consumer in writing of the escalation. 18Tra</t>
+  </si>
+  <si>
+    <t>20Every payment service provider must establish a formal consumer complaint resolution procedure that is easily accessible and clearly communicated to all users. 21Consumer complaints must be acknowle</t>
+  </si>
+  <si>
+    <t>14 Consumer data must not be shared with third parties for marketing purposes without the explicit, documented consent of the consumer.</t>
+  </si>
+  <si>
+    <t>Rejection communications must acknowledge the candidate's application in sufficient detail to demonstrate due consideration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For each year of service with an employer (other than periods of employment as a casual employee of the employer), an employee is entitled to:
+                     (a)  4 weeks of paid annual leave; </t>
+  </si>
+  <si>
+    <t>A person who causes, instructs, induces, aids or permits another person to do an act that is unlawful under Division 1, 2, 2A, 3 or 6 of Part 2 is, for the purposes of this Act, taken also to have don</t>
+  </si>
+  <si>
+    <t>An employer must not request or require an employee to work more than the following number of hours in a week unless the additional hours are reasonable:
+    (a)  for a full‑time employee—38 hours; or</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A modern award or enterprise agreement may include terms providing for the averaging of hours of work over a specified period. The average weekly hours over the period must not exceed:
+               </t>
+  </si>
+  <si>
+    <t>A person must not make an unlawful termination application in relation to conduct if the person is entitled to make a general protections court application in relation to the conduct.</t>
+  </si>
+  <si>
+    <t>A person who has been dismissed must not make an application or complaint of a kind referred to in any one of sections 726 to 732 in relation to the dismissal if any other of those sections applies.</t>
+  </si>
+  <si>
+    <t>The Commission may, by writing under its seal, delegate to:
+                     (a)  a member of the Commission; or
+                     (b)  the Commissioner; or
+                     (c)  a member o</t>
+  </si>
+  <si>
+    <t>Hiring entities are prohibited from gathering, recording, or factoring into any decision-making criteria any information pertaining to a candidate's circumstances outside of their professional qualifi</t>
+  </si>
+  <si>
+    <t>Prior to contacting any provided reference, the employer must issue a 72-hour written notice to the candidate, specifying the name of the reference to be contacted, the method of contact, and the scop</t>
   </si>
 </sst>
 </file>
@@ -513,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -541,13 +622,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -561,13 +642,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -581,13 +662,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -601,13 +682,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -621,13 +702,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -641,13 +722,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -661,13 +742,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -681,13 +762,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -701,13 +782,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -721,13 +802,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -741,13 +822,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -761,13 +842,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -781,13 +862,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -801,13 +882,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -821,13 +902,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -841,13 +922,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -861,13 +942,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -881,13 +962,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -901,13 +982,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -921,13 +1002,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
@@ -941,13 +1022,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E22">
         <v>0.6777</v>
@@ -961,13 +1042,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E23">
         <v>0.6778999999999999</v>
@@ -981,13 +1062,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E24">
         <v>0.6841</v>
@@ -1001,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E25">
         <v>0.6841</v>
@@ -1021,13 +1102,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E26">
         <v>0.6841</v>
@@ -1041,13 +1122,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E27">
         <v>0.6841</v>
@@ -1061,13 +1142,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="E28">
         <v>0.5894</v>
@@ -1081,13 +1162,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E29">
         <v>0.6067</v>
@@ -1101,13 +1182,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E30">
         <v>0.6036</v>
@@ -1121,13 +1202,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E31">
         <v>0.6428</v>
@@ -1141,13 +1222,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="E32">
         <v>0.4052</v>
@@ -1161,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E33">
         <v>0.625</v>
@@ -1181,13 +1262,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E34">
         <v>0.6039</v>
@@ -1201,13 +1282,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="s">
         <v>17</v>
       </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E35">
         <v>0.6194</v>
@@ -1221,13 +1302,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="s">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E36">
         <v>0.6367</v>
@@ -1241,13 +1322,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E37">
         <v>0.6216</v>
@@ -1261,18 +1342,458 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="s">
-        <v>20</v>
+        <v>17</v>
+      </c>
+      <c r="C38">
+        <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E38">
         <v>0.6395999999999999</v>
       </c>
       <c r="F38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39" t="s">
+        <v>65</v>
+      </c>
+      <c r="E39">
+        <v>0.6151</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40">
+        <v>2</v>
+      </c>
+      <c r="D40" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40">
+        <v>0.6411</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41">
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41">
+        <v>0.4462</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42">
+        <v>4</v>
+      </c>
+      <c r="D42" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42">
+        <v>0.5122</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43">
+        <v>0.5894</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>19</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44">
+        <v>0.6067</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45">
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>56</v>
+      </c>
+      <c r="E45">
+        <v>0.6036</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>19</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+      <c r="D46" t="s">
+        <v>57</v>
+      </c>
+      <c r="E46">
+        <v>0.6428</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47">
+        <v>5</v>
+      </c>
+      <c r="D47" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47">
+        <v>0.4052</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>19</v>
+      </c>
+      <c r="C48">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48">
+        <v>0.625</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>60</v>
+      </c>
+      <c r="E49">
+        <v>0.6039</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E50">
+        <v>0.4927</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" t="s">
+        <v>21</v>
+      </c>
+      <c r="D51" t="s">
+        <v>70</v>
+      </c>
+      <c r="E51">
+        <v>0.6346000000000001</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>20</v>
+      </c>
+      <c r="C52" t="s">
+        <v>22</v>
+      </c>
+      <c r="D52" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52">
+        <v>0.3461</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>20</v>
+      </c>
+      <c r="C53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" t="s">
+        <v>72</v>
+      </c>
+      <c r="E53">
+        <v>0.15</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54">
+        <v>0.4212</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C55" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55">
+        <v>0.3107</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56" t="s">
+        <v>75</v>
+      </c>
+      <c r="E56">
+        <v>0.2965</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57">
+        <v>0.2812</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>28</v>
+      </c>
+      <c r="D58" t="s">
+        <v>77</v>
+      </c>
+      <c r="E58">
+        <v>0.2349</v>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>20</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59">
+        <v>0.6031</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>20</v>
+      </c>
+      <c r="C60" t="s">
+        <v>30</v>
+      </c>
+      <c r="D60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60">
+        <v>0.4668</v>
+      </c>
+      <c r="F60" t="b">
         <v>1</v>
       </c>
     </row>

--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="127">
   <si>
     <t>process_hash</t>
   </si>
@@ -40,6 +40,21 @@
     <t>2a605ee07a180f75</t>
   </si>
   <si>
+    <t>82a487c2bf98ebc9</t>
+  </si>
+  <si>
+    <t>1857480f7c237393</t>
+  </si>
+  <si>
+    <t>d1037b5cade27a30</t>
+  </si>
+  <si>
+    <t>ce0b3a040abd6bbc</t>
+  </si>
+  <si>
+    <t>2b2413960ba00370</t>
+  </si>
+  <si>
     <t>synthetic-compliance-rules-#1</t>
   </si>
   <si>
@@ -79,6 +94,18 @@
     <t>sai_internal_hiring_process</t>
   </si>
   <si>
+    <t>sai_travel_insurance_claims_process</t>
+  </si>
+  <si>
+    <t>sai_bank_account_opening_process</t>
+  </si>
+  <si>
+    <t>barrientos_sim_card</t>
+  </si>
+  <si>
+    <t>barritentos_emergencies</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -92,21 +119,6 @@
   </si>
   <si>
     <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
   </si>
   <si>
     <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
@@ -263,6 +275,156 @@
   </si>
   <si>
     <t>Prior to contacting any provided reference, the employer must issue a 72-hour written notice to the candidate, specifying the name of the reference to be contacted, the method of contact, and the scop</t>
+  </si>
+  <si>
+    <t>a:In circumstances where:
+a. your claim arises from an Extraordinary
+Catastrophe;
+b. your claim is fraudulent, or we
+reasonably suspect it is fraudulent;
+c. you do not respond to our reasonable
+inquir</t>
+  </si>
+  <si>
+    <t>b:If you make a claim, then we will tell you: a. about our claims process; b. about any excess amounts you have to cover or pay in relation to your claim; c. about any waiting or no cover periods that</t>
+  </si>
+  <si>
+    <t>c:We will tell you about the progress of your claim at least every 20 Business Days.</t>
+  </si>
+  <si>
+    <t>d:When we assess your claim, we will consider all relevant facts, the terms of your insurance policy and the law.</t>
+  </si>
+  <si>
+    <t>e:When we receive your Complaint, we will acknowledge that we have received it.</t>
+  </si>
+  <si>
+    <t>j:We will require our Employees and Distributors to receive appropriate education and training: a. to provide their services competently; b. to deal with you professionally; and c. about the Code.</t>
+  </si>
+  <si>
+    <t>g:We will not sell you a Consumer Credit Insurance product during the deferred sales period.</t>
+  </si>
+  <si>
+    <t>h:You can take your Complaint to the Australian Financial Complaints Authority at any time and if we do not resolve your Complaint within 30 Calendar Days after we first received your Complaint.</t>
+  </si>
+  <si>
+    <t>k:With effect from 1 January 2025, all travel insurance claims shall be submitted exclusively through the FCPA Portal</t>
+  </si>
+  <si>
+    <t>l:Following successful claim registration, the insurer must send a formal written acknowledgement to the policyholder no later than 2 Business Days after the date of registration.</t>
+  </si>
+  <si>
+    <t>The reporting entity must, as soon as practicable, take reasonable measures to:
+(1)               obtain and verify additional KYC information; or
+(2)               update and verify existing KYC in</t>
+  </si>
+  <si>
+    <t>Customer due diligence procedures (however described) that comply with one or more laws of a foreign country giving effect to the FATF Recommendations relating to customer due diligence and record-kee</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls that are designed to enable the reporting entity to be reasonably satisfied, where a customer is an individual, that the cus</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include a procedure for the reporting entity to collect, at a minimum, the following KYC information about an individual (other than an individual who notifies the reporting en</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include a procedure for the reporting entity to collect at a minimum, the following KYC information about a customer who notifies the reporting entity that he or she is a custo</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to determine whether, in addition to the KYC information referred to in paragraph 4.2.3 or 4.2.4 ab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An AML/CTF program must include a procedure for the reporting entity to verify, at a minimum, the following KYC information about a customer:
+(1)      the customer's full name; and
+(2)      either:
+</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must require that the verification of information collected about a customer be based on:
+(1)      reliable and independent documentation;
+(2)      reliable and independent electr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to determine whether, in addition to the KYC information referred to in paragraph 4.2.6 above, any </t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to respond to any discrepancy that arises in the course of verifying KYC information collected abou</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must require that the reporting entity be satisfied that any document from which the reporting entity verifies KYC information about an individual has not expired (other than in the</t>
+  </si>
+  <si>
+    <t>An AML/CTF program must include appropriate risk‑based systems and controls for the reporting entity to determine:
+(1)      whether the electronic data is reliable and independent, taking into accoun</t>
+  </si>
+  <si>
+    <t>A reporting entity must apply appropriate levels of ongoing customer due diligence in order to identify, mitigate and manage any ML/TF risk associated with customer identities established using self-a</t>
+  </si>
+  <si>
+    <t>If an Australian Privacy Principle entity is an organisation, the entity must not collect personal information (other than sensitive information) unless the information is reasonably necessary for one</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must not collect sensitive information about an individual unless:
+a) the individual consents to the collection of the information and:
+- if the entity is an age</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must collect personal information only by lawful and fair means.</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must collect personal information about an individual only from the individual unless:
+a) if the entity is an agency:
+- the individual consents to the collection</t>
+  </si>
+  <si>
+    <t>An Australian Privacy Principle entity must take such steps (if any) as are reasonable in the circumstances to ensure that the personal information that the entity collects is accurate, up-to-date and</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Australian Privacy Principle entity must take such steps (if any) as are reasonable in the circumstances to ensure that the personal information that the entity uses or discloses is, having regard </t>
+  </si>
+  <si>
+    <t>If an Australian Privacy Principle entity holds personal information, the entity must take such steps as are reasonable in the circumstances to protect the information:
+a) from misuse, interference an</t>
+  </si>
+  <si>
+    <t>If an Australian Privacy Principle entity holds personal information about an individual, the entity must, on request by the individual, give the individual access to the information.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At or before the time or, if that is not practicable, as soon as practicable after, an Australian Privacy Principle entity collects personal information about an individual, the entity must take such </t>
+  </si>
+  <si>
+    <t>If:
+a) an Australian Privacy Principle entity holds personal information about an individual; and
+b) the entity no longer needs the information for any purpose for which the information may be used or</t>
+  </si>
+  <si>
+    <t>The process of phone company must be terminated if it takes more than 30 days for any reason</t>
+  </si>
+  <si>
+    <t>After receiving the customer’s personal information, it is necessary to verify the correctness of their personal information</t>
+  </si>
+  <si>
+    <t>When the customer receives the sim card, the phone company must activate the SIM card so that the customer can use the SIM card normally</t>
+  </si>
+  <si>
+    <t>Before retrieving any kind of personal data from the Data Subject, the Data Controller has to ask the Data Subject for consent</t>
+  </si>
+  <si>
+    <t>Customers with outstanding debt exceeding 50 € are not eligible to receive new SIM cardsIf the third party denies portability, the customer’s personal data must be deleted from the database</t>
+  </si>
+  <si>
+    <t>If local anesthesia is administered and the patient has a high tolerance to anesthesia, additional anesthesia must be administered every 20 minutes</t>
+  </si>
+  <si>
+    <t>Before a surgical intervention, the nurse must obtain the patient’s consent. After obtaining consent, the doctor must conduct a ``time out'' procedure</t>
+  </si>
+  <si>
+    <t>If the patient is over 65 or has more than 5 medications, a doctor must approve discharge before the patient is discharged.</t>
+  </si>
+  <si>
+    <t>Physical examination and blood test are required before making a diagnosis</t>
+  </si>
+  <si>
+    <t>Blood samples must be collected from all patients</t>
   </si>
 </sst>
 </file>
@@ -594,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -622,13 +784,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -642,13 +804,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -662,13 +824,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -682,13 +844,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -702,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -722,13 +884,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -742,13 +904,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -762,13 +924,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -782,13 +944,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -802,13 +964,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -822,13 +984,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C12">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -842,13 +1004,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C13">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -862,13 +1024,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -882,13 +1044,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -902,13 +1064,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -922,13 +1084,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C17">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -942,13 +1104,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -962,13 +1124,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -982,13 +1144,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -1002,13 +1164,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
@@ -1022,13 +1184,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E22">
         <v>0.6777</v>
@@ -1042,13 +1204,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E23">
         <v>0.6778999999999999</v>
@@ -1062,13 +1224,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E24">
         <v>0.6841</v>
@@ -1082,13 +1244,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E25">
         <v>0.6841</v>
@@ -1102,13 +1264,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E26">
         <v>0.6841</v>
@@ -1122,13 +1284,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E27">
         <v>0.6841</v>
@@ -1142,13 +1304,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E28">
         <v>0.5894</v>
@@ -1162,13 +1324,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E29">
         <v>0.6067</v>
@@ -1182,13 +1344,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E30">
         <v>0.6036</v>
@@ -1202,13 +1364,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E31">
         <v>0.6428</v>
@@ -1222,13 +1384,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E32">
         <v>0.4052</v>
@@ -1242,13 +1404,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E33">
         <v>0.625</v>
@@ -1262,13 +1424,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E34">
         <v>0.6039</v>
@@ -1282,13 +1444,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E35">
         <v>0.6194</v>
@@ -1302,13 +1464,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E36">
         <v>0.6367</v>
@@ -1322,13 +1484,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E37">
         <v>0.6216</v>
@@ -1342,13 +1504,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E38">
         <v>0.6395999999999999</v>
@@ -1362,13 +1524,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E39">
         <v>0.6151</v>
@@ -1382,13 +1544,13 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E40">
         <v>0.6411</v>
@@ -1402,13 +1564,13 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E41">
         <v>0.4462</v>
@@ -1422,13 +1584,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E42">
         <v>0.5122</v>
@@ -1442,13 +1604,13 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E43">
         <v>0.5894</v>
@@ -1462,13 +1624,13 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E44">
         <v>0.6067</v>
@@ -1482,13 +1644,13 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E45">
         <v>0.6036</v>
@@ -1502,13 +1664,13 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E46">
         <v>0.6428</v>
@@ -1522,13 +1684,13 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E47">
         <v>0.4052</v>
@@ -1542,13 +1704,13 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C48">
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E48">
         <v>0.625</v>
@@ -1562,13 +1724,13 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E49">
         <v>0.6039</v>
@@ -1582,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E50">
         <v>0.4927</v>
@@ -1602,13 +1764,13 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
-      </c>
-      <c r="C51" t="s">
-        <v>21</v>
+        <v>25</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E51">
         <v>0.6346000000000001</v>
@@ -1622,13 +1784,13 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E52">
         <v>0.3461</v>
@@ -1642,13 +1804,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>20</v>
-      </c>
-      <c r="C53" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="C53">
+        <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E53">
         <v>0.15</v>
@@ -1662,13 +1824,13 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>20</v>
-      </c>
-      <c r="C54" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="C54">
+        <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E54">
         <v>0.4212</v>
@@ -1682,13 +1844,13 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>20</v>
-      </c>
-      <c r="C55" t="s">
         <v>25</v>
       </c>
+      <c r="C55">
+        <v>5</v>
+      </c>
       <c r="D55" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E55">
         <v>0.3107</v>
@@ -1702,13 +1864,13 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="C56">
+        <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E56">
         <v>0.2965</v>
@@ -1722,13 +1884,13 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>20</v>
-      </c>
-      <c r="C57" t="s">
-        <v>27</v>
+        <v>25</v>
+      </c>
+      <c r="C57">
+        <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E57">
         <v>0.2812</v>
@@ -1742,13 +1904,13 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
-      </c>
-      <c r="C58" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="C58">
+        <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E58">
         <v>0.2349</v>
@@ -1762,13 +1924,13 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" t="s">
-        <v>29</v>
+        <v>25</v>
+      </c>
+      <c r="C59">
+        <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E59">
         <v>0.6031</v>
@@ -1782,18 +1944,1078 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="C60">
+        <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E60">
         <v>0.4668</v>
       </c>
       <c r="F60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61">
+        <v>0.4043</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>8</v>
+      </c>
+      <c r="B62" t="s">
+        <v>26</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+      <c r="D62" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62">
+        <v>0.496</v>
+      </c>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>8</v>
+      </c>
+      <c r="B63" t="s">
+        <v>26</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>86</v>
+      </c>
+      <c r="E63">
+        <v>0.4781</v>
+      </c>
+      <c r="F63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64">
+        <v>4</v>
+      </c>
+      <c r="D64" t="s">
+        <v>87</v>
+      </c>
+      <c r="E64">
+        <v>0.5125</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C65">
+        <v>5</v>
+      </c>
+      <c r="D65" t="s">
+        <v>88</v>
+      </c>
+      <c r="E65">
+        <v>0.3548</v>
+      </c>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" t="s">
+        <v>26</v>
+      </c>
+      <c r="C66">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66">
+        <v>0.2212</v>
+      </c>
+      <c r="F66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
+        <v>26</v>
+      </c>
+      <c r="C67">
+        <v>7</v>
+      </c>
+      <c r="D67" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67">
+        <v>0.3205</v>
+      </c>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" t="s">
+        <v>26</v>
+      </c>
+      <c r="C68">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68">
+        <v>0.2504</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" t="s">
+        <v>26</v>
+      </c>
+      <c r="C69">
+        <v>9</v>
+      </c>
+      <c r="D69" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69">
+        <v>0.51</v>
+      </c>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>8</v>
+      </c>
+      <c r="B70" t="s">
+        <v>26</v>
+      </c>
+      <c r="C70">
+        <v>10</v>
+      </c>
+      <c r="D70" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70">
+        <v>0.4057</v>
+      </c>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s">
+        <v>26</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+      <c r="D71" t="s">
+        <v>84</v>
+      </c>
+      <c r="E71">
+        <v>0.6163999999999999</v>
+      </c>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" t="s">
+        <v>26</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="D72" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72">
+        <v>0.5685</v>
+      </c>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>86</v>
+      </c>
+      <c r="E73">
+        <v>0.6151</v>
+      </c>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" t="s">
+        <v>26</v>
+      </c>
+      <c r="C74">
+        <v>4</v>
+      </c>
+      <c r="D74" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74">
+        <v>0.6232</v>
+      </c>
+      <c r="F74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" t="s">
+        <v>26</v>
+      </c>
+      <c r="C75">
+        <v>5</v>
+      </c>
+      <c r="D75" t="s">
+        <v>88</v>
+      </c>
+      <c r="E75">
+        <v>0.5322</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
+        <v>26</v>
+      </c>
+      <c r="C76">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76">
+        <v>0.3512</v>
+      </c>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" t="s">
+        <v>26</v>
+      </c>
+      <c r="C77">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>90</v>
+      </c>
+      <c r="E77">
+        <v>0.4761</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" t="s">
+        <v>26</v>
+      </c>
+      <c r="C78">
+        <v>8</v>
+      </c>
+      <c r="D78" t="s">
+        <v>91</v>
+      </c>
+      <c r="E78">
+        <v>0.481</v>
+      </c>
+      <c r="F78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B79" t="s">
+        <v>26</v>
+      </c>
+      <c r="C79">
+        <v>9</v>
+      </c>
+      <c r="D79" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79">
+        <v>0.5723</v>
+      </c>
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80">
+        <v>10</v>
+      </c>
+      <c r="D80" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80">
+        <v>0.6477000000000001</v>
+      </c>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
+        <v>27</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81" t="s">
+        <v>94</v>
+      </c>
+      <c r="E81">
+        <v>0.4285</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82">
+        <v>2</v>
+      </c>
+      <c r="D82" t="s">
+        <v>95</v>
+      </c>
+      <c r="E82">
+        <v>0.5831</v>
+      </c>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" t="s">
+        <v>27</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>96</v>
+      </c>
+      <c r="E83">
+        <v>0.3756</v>
+      </c>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84">
+        <v>4</v>
+      </c>
+      <c r="D84" t="s">
+        <v>97</v>
+      </c>
+      <c r="E84">
+        <v>0.4707</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85">
+        <v>5</v>
+      </c>
+      <c r="D85" t="s">
+        <v>98</v>
+      </c>
+      <c r="E85">
+        <v>0.4945</v>
+      </c>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>10</v>
+      </c>
+      <c r="B86" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s">
+        <v>99</v>
+      </c>
+      <c r="E86">
+        <v>0.3551</v>
+      </c>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>10</v>
+      </c>
+      <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87">
+        <v>7</v>
+      </c>
+      <c r="D87" t="s">
+        <v>100</v>
+      </c>
+      <c r="E87">
+        <v>0.5426</v>
+      </c>
+      <c r="F87" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>10</v>
+      </c>
+      <c r="B88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88">
+        <v>8</v>
+      </c>
+      <c r="D88" t="s">
+        <v>101</v>
+      </c>
+      <c r="E88">
+        <v>0.5185999999999999</v>
+      </c>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89">
+        <v>9</v>
+      </c>
+      <c r="D89" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89">
+        <v>0.3634</v>
+      </c>
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>10</v>
+      </c>
+      <c r="B90" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90">
+        <v>10</v>
+      </c>
+      <c r="D90" t="s">
+        <v>103</v>
+      </c>
+      <c r="E90">
+        <v>0.4161</v>
+      </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>10</v>
+      </c>
+      <c r="B91" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91">
+        <v>11</v>
+      </c>
+      <c r="D91" t="s">
+        <v>104</v>
+      </c>
+      <c r="E91">
+        <v>0.2871</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>10</v>
+      </c>
+      <c r="B92" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92">
+        <v>12</v>
+      </c>
+      <c r="D92" t="s">
+        <v>105</v>
+      </c>
+      <c r="E92">
+        <v>0.506</v>
+      </c>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>10</v>
+      </c>
+      <c r="B93" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93">
+        <v>13</v>
+      </c>
+      <c r="D93" t="s">
+        <v>106</v>
+      </c>
+      <c r="E93">
+        <v>0.4668</v>
+      </c>
+      <c r="F93" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>10</v>
+      </c>
+      <c r="B94" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94">
+        <v>14</v>
+      </c>
+      <c r="D94" t="s">
+        <v>107</v>
+      </c>
+      <c r="E94">
+        <v>0.3633</v>
+      </c>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>10</v>
+      </c>
+      <c r="B95" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95">
+        <v>0.3922</v>
+      </c>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>10</v>
+      </c>
+      <c r="B96" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96">
+        <v>16</v>
+      </c>
+      <c r="D96" t="s">
+        <v>109</v>
+      </c>
+      <c r="E96">
+        <v>0.4302</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>10</v>
+      </c>
+      <c r="B97" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97">
+        <v>17</v>
+      </c>
+      <c r="D97" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97">
+        <v>0.4779</v>
+      </c>
+      <c r="F97" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>10</v>
+      </c>
+      <c r="B98" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98">
+        <v>18</v>
+      </c>
+      <c r="D98" t="s">
+        <v>111</v>
+      </c>
+      <c r="E98">
+        <v>0.4652</v>
+      </c>
+      <c r="F98" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99">
+        <v>19</v>
+      </c>
+      <c r="D99" t="s">
+        <v>112</v>
+      </c>
+      <c r="E99">
+        <v>0.4672</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" t="s">
+        <v>27</v>
+      </c>
+      <c r="C100">
+        <v>20</v>
+      </c>
+      <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100">
+        <v>0.4137</v>
+      </c>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" t="s">
+        <v>27</v>
+      </c>
+      <c r="C101">
+        <v>21</v>
+      </c>
+      <c r="D101" t="s">
+        <v>114</v>
+      </c>
+      <c r="E101">
+        <v>0.3759</v>
+      </c>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>10</v>
+      </c>
+      <c r="B102" t="s">
+        <v>27</v>
+      </c>
+      <c r="C102">
+        <v>22</v>
+      </c>
+      <c r="D102" t="s">
+        <v>115</v>
+      </c>
+      <c r="E102">
+        <v>0.3841</v>
+      </c>
+      <c r="F102" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103">
+        <v>23</v>
+      </c>
+      <c r="D103" t="s">
+        <v>116</v>
+      </c>
+      <c r="E103">
+        <v>0.377</v>
+      </c>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104" t="s">
+        <v>117</v>
+      </c>
+      <c r="E104">
+        <v>0.589</v>
+      </c>
+      <c r="F104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" t="s">
+        <v>28</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105">
+        <v>0.5769</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" t="s">
+        <v>28</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="s">
+        <v>119</v>
+      </c>
+      <c r="E106">
+        <v>0.8023</v>
+      </c>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" t="s">
+        <v>28</v>
+      </c>
+      <c r="C107">
+        <v>4</v>
+      </c>
+      <c r="D107" t="s">
+        <v>120</v>
+      </c>
+      <c r="E107">
+        <v>0.6107</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" t="s">
+        <v>28</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+      <c r="D108" t="s">
+        <v>121</v>
+      </c>
+      <c r="E108">
+        <v>0.5578</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>12</v>
+      </c>
+      <c r="B109" t="s">
+        <v>29</v>
+      </c>
+      <c r="C109" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" t="s">
+        <v>122</v>
+      </c>
+      <c r="E109">
+        <v>0.525</v>
+      </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" t="s">
+        <v>29</v>
+      </c>
+      <c r="C110" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" t="s">
+        <v>123</v>
+      </c>
+      <c r="E110">
+        <v>0.6331</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>12</v>
+      </c>
+      <c r="B111" t="s">
+        <v>29</v>
+      </c>
+      <c r="C111" t="s">
+        <v>32</v>
+      </c>
+      <c r="D111" t="s">
+        <v>124</v>
+      </c>
+      <c r="E111">
+        <v>0.6157</v>
+      </c>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>12</v>
+      </c>
+      <c r="B112" t="s">
+        <v>29</v>
+      </c>
+      <c r="C112" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" t="s">
+        <v>125</v>
+      </c>
+      <c r="E112">
+        <v>0.5907</v>
+      </c>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>12</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+      <c r="C113" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" t="s">
+        <v>126</v>
+      </c>
+      <c r="E113">
+        <v>0.5887</v>
+      </c>
+      <c r="F113" t="b">
         <v>1</v>
       </c>
     </row>

--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="143">
   <si>
     <t>process_hash</t>
   </si>
@@ -55,6 +55,18 @@
     <t>2b2413960ba00370</t>
   </si>
   <si>
+    <t>de3da52a4445c58b</t>
+  </si>
+  <si>
+    <t>1f1d35c4b58987f3</t>
+  </si>
+  <si>
+    <t>fc99b15abc32168f</t>
+  </si>
+  <si>
+    <t>d9bbe9c16b24a1ef</t>
+  </si>
+  <si>
     <t>synthetic-compliance-rules-#1</t>
   </si>
   <si>
@@ -104,6 +116,9 @@
   </si>
   <si>
     <t>barritentos_emergencies</t>
+  </si>
+  <si>
+    <t>claude_merchant_onboarding</t>
   </si>
   <si>
     <t>1</t>
@@ -425,6 +440,39 @@
   </si>
   <si>
     <t>Blood samples must be collected from all patients</t>
+  </si>
+  <si>
+    <t>7All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
+  </si>
+  <si>
+    <t>8The identity verification process must include validation of the merchant's legal registration, beneficial ownership structure, and principal place of business.</t>
+  </si>
+  <si>
+    <t>17Payment service providers shall establish and maintain a real-time transaction monitoring system capable of detecting anomalous or potentially fraudulent activity.</t>
+  </si>
+  <si>
+    <t>10Where a merchant operates in a high-risk category as defined in Annex II, the payment service provider shall apply enhanced due diligence measures appropriate to the level of risk.</t>
+  </si>
+  <si>
+    <t>9Payment service providers are prohibited from onboarding any merchant that appears on a government-maintained sanctions or exclusion list.</t>
+  </si>
+  <si>
+    <t>13Payment service providers shall implement adequate technical and organizational safeguards to protect consumer data against unauthorized access, disclosure, or destruction.</t>
+  </si>
+  <si>
+    <t>11Verification records shall be retained for a minimum period of seven years from the date of merchant account closure.</t>
+  </si>
+  <si>
+    <t>22If a complaint cannot be resolved within the prescribed timeframe, the provider shall escalate the matter to the Consumer Mediation Office and inform the consumer in writing of the escalation.</t>
+  </si>
+  <si>
+    <t>18Transactions exceeding the threshold amount specified in Annex III must be flagged for manual review and reported to the Financial Intelligence Unit within five business days.</t>
+  </si>
+  <si>
+    <t>20Every payment service provider must establish a formal consumer complaint resolution procedure that is easily accessible and clearly communicated to all users.</t>
+  </si>
+  <si>
+    <t>21Consumer complaints must be acknowledged within two business days and resolved within 30 calendar days of receipt.</t>
   </si>
 </sst>
 </file>
@@ -756,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -784,13 +832,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -804,13 +852,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -824,13 +872,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -844,13 +892,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -864,13 +912,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -884,13 +932,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -904,13 +952,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -924,13 +972,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -944,13 +992,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -964,13 +1012,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -984,13 +1032,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -1004,13 +1052,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -1024,13 +1072,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -1044,13 +1092,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -1064,13 +1112,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C16">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -1084,13 +1132,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C17">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -1104,13 +1152,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -1124,13 +1172,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -1144,13 +1192,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -1164,13 +1212,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
@@ -1184,13 +1232,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E22">
         <v>0.6777</v>
@@ -1204,13 +1252,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E23">
         <v>0.6778999999999999</v>
@@ -1224,13 +1272,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E24">
         <v>0.6841</v>
@@ -1244,13 +1292,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E25">
         <v>0.6841</v>
@@ -1264,13 +1312,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E26">
         <v>0.6841</v>
@@ -1284,13 +1332,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E27">
         <v>0.6841</v>
@@ -1304,13 +1352,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E28">
         <v>0.5894</v>
@@ -1324,13 +1372,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E29">
         <v>0.6067</v>
@@ -1344,13 +1392,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E30">
         <v>0.6036</v>
@@ -1364,13 +1412,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E31">
         <v>0.6428</v>
@@ -1384,13 +1432,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E32">
         <v>0.4052</v>
@@ -1404,13 +1452,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E33">
         <v>0.625</v>
@@ -1424,13 +1472,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E34">
         <v>0.6039</v>
@@ -1444,13 +1492,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E35">
         <v>0.6194</v>
@@ -1464,13 +1512,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E36">
         <v>0.6367</v>
@@ -1484,13 +1532,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E37">
         <v>0.6216</v>
@@ -1504,13 +1552,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E38">
         <v>0.6395999999999999</v>
@@ -1524,13 +1572,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E39">
         <v>0.6151</v>
@@ -1544,13 +1592,13 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E40">
         <v>0.6411</v>
@@ -1564,13 +1612,13 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E41">
         <v>0.4462</v>
@@ -1584,13 +1632,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E42">
         <v>0.5122</v>
@@ -1604,13 +1652,13 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E43">
         <v>0.5894</v>
@@ -1624,13 +1672,13 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E44">
         <v>0.6067</v>
@@ -1644,13 +1692,13 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E45">
         <v>0.6036</v>
@@ -1664,13 +1712,13 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E46">
         <v>0.6428</v>
@@ -1684,13 +1732,13 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E47">
         <v>0.4052</v>
@@ -1704,13 +1752,13 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C48">
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E48">
         <v>0.625</v>
@@ -1724,13 +1772,13 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E49">
         <v>0.6039</v>
@@ -1744,13 +1792,13 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E50">
         <v>0.4927</v>
@@ -1764,13 +1812,13 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E51">
         <v>0.6346000000000001</v>
@@ -1784,13 +1832,13 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E52">
         <v>0.3461</v>
@@ -1804,13 +1852,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E53">
         <v>0.15</v>
@@ -1824,13 +1872,13 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E54">
         <v>0.4212</v>
@@ -1844,13 +1892,13 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C55">
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E55">
         <v>0.3107</v>
@@ -1864,13 +1912,13 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E56">
         <v>0.2965</v>
@@ -1884,13 +1932,13 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C57">
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E57">
         <v>0.2812</v>
@@ -1904,13 +1952,13 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C58">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E58">
         <v>0.2349</v>
@@ -1924,13 +1972,13 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C59">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E59">
         <v>0.6031</v>
@@ -1944,13 +1992,13 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C60">
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E60">
         <v>0.4668</v>
@@ -1964,13 +2012,13 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E61">
         <v>0.4043</v>
@@ -1984,13 +2032,13 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E62">
         <v>0.496</v>
@@ -2004,13 +2052,13 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E63">
         <v>0.4781</v>
@@ -2024,13 +2072,13 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C64">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E64">
         <v>0.5125</v>
@@ -2044,13 +2092,13 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C65">
         <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E65">
         <v>0.3548</v>
@@ -2064,13 +2112,13 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C66">
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E66">
         <v>0.2212</v>
@@ -2084,13 +2132,13 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C67">
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E67">
         <v>0.3205</v>
@@ -2104,13 +2152,13 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C68">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E68">
         <v>0.2504</v>
@@ -2124,13 +2172,13 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C69">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E69">
         <v>0.51</v>
@@ -2144,13 +2192,13 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C70">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E70">
         <v>0.4057</v>
@@ -2164,13 +2212,13 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E71">
         <v>0.6163999999999999</v>
@@ -2184,13 +2232,13 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E72">
         <v>0.5685</v>
@@ -2204,13 +2252,13 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E73">
         <v>0.6151</v>
@@ -2224,13 +2272,13 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C74">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E74">
         <v>0.6232</v>
@@ -2244,13 +2292,13 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C75">
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E75">
         <v>0.5322</v>
@@ -2264,13 +2312,13 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C76">
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E76">
         <v>0.3512</v>
@@ -2284,13 +2332,13 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C77">
         <v>7</v>
       </c>
       <c r="D77" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E77">
         <v>0.4761</v>
@@ -2304,13 +2352,13 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C78">
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E78">
         <v>0.481</v>
@@ -2324,13 +2372,13 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C79">
         <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E79">
         <v>0.5723</v>
@@ -2344,13 +2392,13 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C80">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="E80">
         <v>0.6477000000000001</v>
@@ -2364,13 +2412,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E81">
         <v>0.4285</v>
@@ -2384,13 +2432,13 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E82">
         <v>0.5831</v>
@@ -2404,13 +2452,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E83">
         <v>0.3756</v>
@@ -2424,13 +2472,13 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C84">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E84">
         <v>0.4707</v>
@@ -2444,13 +2492,13 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C85">
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E85">
         <v>0.4945</v>
@@ -2464,13 +2512,13 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C86">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E86">
         <v>0.3551</v>
@@ -2484,13 +2532,13 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C87">
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E87">
         <v>0.5426</v>
@@ -2504,13 +2552,13 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C88">
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E88">
         <v>0.5185999999999999</v>
@@ -2524,13 +2572,13 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C89">
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E89">
         <v>0.3634</v>
@@ -2544,13 +2592,13 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C90">
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E90">
         <v>0.4161</v>
@@ -2564,13 +2612,13 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C91">
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E91">
         <v>0.2871</v>
@@ -2584,13 +2632,13 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C92">
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E92">
         <v>0.506</v>
@@ -2604,13 +2652,13 @@
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C93">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E93">
         <v>0.4668</v>
@@ -2624,13 +2672,13 @@
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C94">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E94">
         <v>0.3633</v>
@@ -2644,13 +2692,13 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C95">
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E95">
         <v>0.3922</v>
@@ -2664,13 +2712,13 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C96">
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E96">
         <v>0.4302</v>
@@ -2684,13 +2732,13 @@
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C97">
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E97">
         <v>0.4779</v>
@@ -2704,13 +2752,13 @@
         <v>10</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C98">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E98">
         <v>0.4652</v>
@@ -2724,13 +2772,13 @@
         <v>10</v>
       </c>
       <c r="B99" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C99">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E99">
         <v>0.4672</v>
@@ -2744,13 +2792,13 @@
         <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C100">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E100">
         <v>0.4137</v>
@@ -2764,13 +2812,13 @@
         <v>10</v>
       </c>
       <c r="B101" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C101">
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E101">
         <v>0.3759</v>
@@ -2784,13 +2832,13 @@
         <v>10</v>
       </c>
       <c r="B102" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C102">
         <v>22</v>
       </c>
       <c r="D102" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E102">
         <v>0.3841</v>
@@ -2804,13 +2852,13 @@
         <v>10</v>
       </c>
       <c r="B103" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C103">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E103">
         <v>0.377</v>
@@ -2824,13 +2872,13 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E104">
         <v>0.589</v>
@@ -2844,13 +2892,13 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E105">
         <v>0.5769</v>
@@ -2864,13 +2912,13 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E106">
         <v>0.8023</v>
@@ -2884,13 +2932,13 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C107">
         <v>4</v>
       </c>
       <c r="D107" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="E107">
         <v>0.6107</v>
@@ -2904,13 +2952,13 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C108">
         <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E108">
         <v>0.5578</v>
@@ -2924,13 +2972,13 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>29</v>
-      </c>
-      <c r="C109" t="s">
-        <v>30</v>
+        <v>33</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E109">
         <v>0.525</v>
@@ -2944,13 +2992,13 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
-      </c>
-      <c r="C110" t="s">
-        <v>31</v>
+        <v>33</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="E110">
         <v>0.6331</v>
@@ -2964,13 +3012,13 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>29</v>
-      </c>
-      <c r="C111" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="C111">
+        <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E111">
         <v>0.6157</v>
@@ -2984,13 +3032,13 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>29</v>
-      </c>
-      <c r="C112" t="s">
         <v>33</v>
       </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
       <c r="D112" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="E112">
         <v>0.5907</v>
@@ -3004,18 +3052,938 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
-      </c>
-      <c r="C113" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+      <c r="C113">
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E113">
         <v>0.5887</v>
       </c>
       <c r="F113" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>13</v>
+      </c>
+      <c r="B114" t="s">
+        <v>30</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114" t="s">
+        <v>89</v>
+      </c>
+      <c r="E114">
+        <v>0.4681</v>
+      </c>
+      <c r="F114" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>13</v>
+      </c>
+      <c r="B115" t="s">
+        <v>30</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>90</v>
+      </c>
+      <c r="E115">
+        <v>0.5196</v>
+      </c>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" t="s">
+        <v>30</v>
+      </c>
+      <c r="C116">
+        <v>3</v>
+      </c>
+      <c r="D116" t="s">
+        <v>91</v>
+      </c>
+      <c r="E116">
+        <v>0.4807</v>
+      </c>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>13</v>
+      </c>
+      <c r="B117" t="s">
+        <v>30</v>
+      </c>
+      <c r="C117">
+        <v>4</v>
+      </c>
+      <c r="D117" t="s">
+        <v>92</v>
+      </c>
+      <c r="E117">
+        <v>0.5272</v>
+      </c>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" t="s">
+        <v>30</v>
+      </c>
+      <c r="C118">
+        <v>5</v>
+      </c>
+      <c r="D118" t="s">
+        <v>93</v>
+      </c>
+      <c r="E118">
+        <v>0.4035</v>
+      </c>
+      <c r="F118" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>13</v>
+      </c>
+      <c r="B119" t="s">
+        <v>30</v>
+      </c>
+      <c r="C119">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>94</v>
+      </c>
+      <c r="E119">
+        <v>0.2197</v>
+      </c>
+      <c r="F119" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>13</v>
+      </c>
+      <c r="B120" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120">
+        <v>7</v>
+      </c>
+      <c r="D120" t="s">
+        <v>95</v>
+      </c>
+      <c r="E120">
+        <v>0.3409</v>
+      </c>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>13</v>
+      </c>
+      <c r="B121" t="s">
+        <v>30</v>
+      </c>
+      <c r="C121">
+        <v>8</v>
+      </c>
+      <c r="D121" t="s">
+        <v>96</v>
+      </c>
+      <c r="E121">
+        <v>0.306</v>
+      </c>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>13</v>
+      </c>
+      <c r="B122" t="s">
+        <v>30</v>
+      </c>
+      <c r="C122">
+        <v>9</v>
+      </c>
+      <c r="D122" t="s">
+        <v>97</v>
+      </c>
+      <c r="E122">
+        <v>0.5057</v>
+      </c>
+      <c r="F122" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
+      <c r="A123" t="s">
+        <v>13</v>
+      </c>
+      <c r="B123" t="s">
+        <v>30</v>
+      </c>
+      <c r="C123">
+        <v>10</v>
+      </c>
+      <c r="D123" t="s">
+        <v>98</v>
+      </c>
+      <c r="E123">
+        <v>0.391</v>
+      </c>
+      <c r="F123" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
+      <c r="A124" t="s">
+        <v>14</v>
+      </c>
+      <c r="B124" t="s">
+        <v>30</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124" t="s">
+        <v>89</v>
+      </c>
+      <c r="E124">
+        <v>0.4744</v>
+      </c>
+      <c r="F124" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
+      <c r="A125" t="s">
+        <v>14</v>
+      </c>
+      <c r="B125" t="s">
+        <v>30</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+      <c r="D125" t="s">
+        <v>90</v>
+      </c>
+      <c r="E125">
+        <v>0.5164</v>
+      </c>
+      <c r="F125" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
+      <c r="A126" t="s">
+        <v>14</v>
+      </c>
+      <c r="B126" t="s">
+        <v>30</v>
+      </c>
+      <c r="C126">
+        <v>3</v>
+      </c>
+      <c r="D126" t="s">
+        <v>91</v>
+      </c>
+      <c r="E126">
+        <v>0.4936</v>
+      </c>
+      <c r="F126" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
+      <c r="A127" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127">
+        <v>4</v>
+      </c>
+      <c r="D127" t="s">
+        <v>92</v>
+      </c>
+      <c r="E127">
+        <v>0.5272</v>
+      </c>
+      <c r="F127" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="A128" t="s">
+        <v>14</v>
+      </c>
+      <c r="B128" t="s">
+        <v>30</v>
+      </c>
+      <c r="C128">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>93</v>
+      </c>
+      <c r="E128">
+        <v>0.3482</v>
+      </c>
+      <c r="F128" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
+      <c r="A129" t="s">
+        <v>14</v>
+      </c>
+      <c r="B129" t="s">
+        <v>30</v>
+      </c>
+      <c r="C129">
+        <v>6</v>
+      </c>
+      <c r="D129" t="s">
+        <v>94</v>
+      </c>
+      <c r="E129">
+        <v>0.2297</v>
+      </c>
+      <c r="F129" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
+      <c r="A130" t="s">
+        <v>14</v>
+      </c>
+      <c r="B130" t="s">
+        <v>30</v>
+      </c>
+      <c r="C130">
+        <v>7</v>
+      </c>
+      <c r="D130" t="s">
+        <v>95</v>
+      </c>
+      <c r="E130">
+        <v>0.3378</v>
+      </c>
+      <c r="F130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
+      <c r="A131" t="s">
+        <v>14</v>
+      </c>
+      <c r="B131" t="s">
+        <v>30</v>
+      </c>
+      <c r="C131">
+        <v>8</v>
+      </c>
+      <c r="D131" t="s">
+        <v>96</v>
+      </c>
+      <c r="E131">
+        <v>0.3239</v>
+      </c>
+      <c r="F131" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="A132" t="s">
+        <v>14</v>
+      </c>
+      <c r="B132" t="s">
+        <v>30</v>
+      </c>
+      <c r="C132">
+        <v>9</v>
+      </c>
+      <c r="D132" t="s">
+        <v>97</v>
+      </c>
+      <c r="E132">
+        <v>0.5134</v>
+      </c>
+      <c r="F132" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="A133" t="s">
+        <v>14</v>
+      </c>
+      <c r="B133" t="s">
+        <v>30</v>
+      </c>
+      <c r="C133">
+        <v>10</v>
+      </c>
+      <c r="D133" t="s">
+        <v>98</v>
+      </c>
+      <c r="E133">
+        <v>0.4012</v>
+      </c>
+      <c r="F133" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>30</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>89</v>
+      </c>
+      <c r="E134">
+        <v>0.4637</v>
+      </c>
+      <c r="F134" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>30</v>
+      </c>
+      <c r="C135">
+        <v>2</v>
+      </c>
+      <c r="D135" t="s">
+        <v>90</v>
+      </c>
+      <c r="E135">
+        <v>0.5274</v>
+      </c>
+      <c r="F135" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136" t="s">
+        <v>91</v>
+      </c>
+      <c r="E136">
+        <v>0.466</v>
+      </c>
+      <c r="F136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>30</v>
+      </c>
+      <c r="C137">
+        <v>4</v>
+      </c>
+      <c r="D137" t="s">
+        <v>92</v>
+      </c>
+      <c r="E137">
+        <v>0.4992</v>
+      </c>
+      <c r="F137" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>30</v>
+      </c>
+      <c r="C138">
+        <v>5</v>
+      </c>
+      <c r="D138" t="s">
+        <v>93</v>
+      </c>
+      <c r="E138">
+        <v>0.3147</v>
+      </c>
+      <c r="F138" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>30</v>
+      </c>
+      <c r="C139">
+        <v>6</v>
+      </c>
+      <c r="D139" t="s">
+        <v>94</v>
+      </c>
+      <c r="E139">
+        <v>0.2325</v>
+      </c>
+      <c r="F139" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>30</v>
+      </c>
+      <c r="C140">
+        <v>7</v>
+      </c>
+      <c r="D140" t="s">
+        <v>95</v>
+      </c>
+      <c r="E140">
+        <v>0.3077</v>
+      </c>
+      <c r="F140" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C141">
+        <v>8</v>
+      </c>
+      <c r="D141" t="s">
+        <v>96</v>
+      </c>
+      <c r="E141">
+        <v>0.3327</v>
+      </c>
+      <c r="F141" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>30</v>
+      </c>
+      <c r="C142">
+        <v>9</v>
+      </c>
+      <c r="D142" t="s">
+        <v>97</v>
+      </c>
+      <c r="E142">
+        <v>0.5164</v>
+      </c>
+      <c r="F142" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>30</v>
+      </c>
+      <c r="C143">
+        <v>10</v>
+      </c>
+      <c r="D143" t="s">
+        <v>98</v>
+      </c>
+      <c r="E143">
+        <v>0.4241</v>
+      </c>
+      <c r="F143" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
+      <c r="A144" t="s">
+        <v>6</v>
+      </c>
+      <c r="B144" t="s">
+        <v>34</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144" t="s">
+        <v>132</v>
+      </c>
+      <c r="E144">
+        <v>0.5915</v>
+      </c>
+      <c r="F144" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" t="s">
+        <v>6</v>
+      </c>
+      <c r="B145" t="s">
+        <v>34</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+      <c r="D145" t="s">
+        <v>133</v>
+      </c>
+      <c r="E145">
+        <v>0.594</v>
+      </c>
+      <c r="F145" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" t="s">
+        <v>6</v>
+      </c>
+      <c r="B146" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146">
+        <v>3</v>
+      </c>
+      <c r="D146" t="s">
+        <v>134</v>
+      </c>
+      <c r="E146">
+        <v>0.6373</v>
+      </c>
+      <c r="F146" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" t="s">
+        <v>6</v>
+      </c>
+      <c r="B147" t="s">
+        <v>34</v>
+      </c>
+      <c r="C147">
+        <v>4</v>
+      </c>
+      <c r="D147" t="s">
+        <v>135</v>
+      </c>
+      <c r="E147">
+        <v>0.7056</v>
+      </c>
+      <c r="F147" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" t="s">
+        <v>6</v>
+      </c>
+      <c r="B148" t="s">
+        <v>34</v>
+      </c>
+      <c r="C148">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>136</v>
+      </c>
+      <c r="E148">
+        <v>0.6233</v>
+      </c>
+      <c r="F148" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" t="s">
+        <v>6</v>
+      </c>
+      <c r="B149" t="s">
+        <v>34</v>
+      </c>
+      <c r="C149">
+        <v>6</v>
+      </c>
+      <c r="D149" t="s">
+        <v>137</v>
+      </c>
+      <c r="E149">
+        <v>0.5113</v>
+      </c>
+      <c r="F149" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" t="s">
+        <v>6</v>
+      </c>
+      <c r="B150" t="s">
+        <v>34</v>
+      </c>
+      <c r="C150">
+        <v>7</v>
+      </c>
+      <c r="D150" t="s">
+        <v>138</v>
+      </c>
+      <c r="E150">
+        <v>0.3871</v>
+      </c>
+      <c r="F150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" t="s">
+        <v>6</v>
+      </c>
+      <c r="B151" t="s">
+        <v>34</v>
+      </c>
+      <c r="C151">
+        <v>8</v>
+      </c>
+      <c r="D151" t="s">
+        <v>139</v>
+      </c>
+      <c r="E151">
+        <v>0.375</v>
+      </c>
+      <c r="F151" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" t="s">
+        <v>6</v>
+      </c>
+      <c r="B152" t="s">
+        <v>34</v>
+      </c>
+      <c r="C152">
+        <v>9</v>
+      </c>
+      <c r="D152" t="s">
+        <v>140</v>
+      </c>
+      <c r="E152">
+        <v>0.4379</v>
+      </c>
+      <c r="F152" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" t="s">
+        <v>6</v>
+      </c>
+      <c r="B153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C153">
+        <v>10</v>
+      </c>
+      <c r="D153" t="s">
+        <v>141</v>
+      </c>
+      <c r="E153">
+        <v>0.5532</v>
+      </c>
+      <c r="F153" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" t="s">
+        <v>6</v>
+      </c>
+      <c r="B154" t="s">
+        <v>34</v>
+      </c>
+      <c r="C154">
+        <v>11</v>
+      </c>
+      <c r="D154" t="s">
+        <v>142</v>
+      </c>
+      <c r="E154">
+        <v>0.3674</v>
+      </c>
+      <c r="F154" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" t="s">
+        <v>16</v>
+      </c>
+      <c r="B155" t="s">
+        <v>32</v>
+      </c>
+      <c r="C155" t="s">
+        <v>35</v>
+      </c>
+      <c r="D155" t="s">
+        <v>122</v>
+      </c>
+      <c r="E155">
+        <v>0.5351</v>
+      </c>
+      <c r="F155" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" t="s">
+        <v>16</v>
+      </c>
+      <c r="B156" t="s">
+        <v>32</v>
+      </c>
+      <c r="C156" t="s">
+        <v>36</v>
+      </c>
+      <c r="D156" t="s">
+        <v>123</v>
+      </c>
+      <c r="E156">
+        <v>0.5658</v>
+      </c>
+      <c r="F156" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" t="s">
+        <v>16</v>
+      </c>
+      <c r="B157" t="s">
+        <v>32</v>
+      </c>
+      <c r="C157" t="s">
+        <v>37</v>
+      </c>
+      <c r="D157" t="s">
+        <v>124</v>
+      </c>
+      <c r="E157">
+        <v>0.8372000000000001</v>
+      </c>
+      <c r="F157" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" t="s">
+        <v>16</v>
+      </c>
+      <c r="B158" t="s">
+        <v>32</v>
+      </c>
+      <c r="C158" t="s">
+        <v>38</v>
+      </c>
+      <c r="D158" t="s">
+        <v>125</v>
+      </c>
+      <c r="E158">
+        <v>0.6856</v>
+      </c>
+      <c r="F158" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" t="s">
+        <v>16</v>
+      </c>
+      <c r="B159" t="s">
+        <v>32</v>
+      </c>
+      <c r="C159" t="s">
+        <v>39</v>
+      </c>
+      <c r="D159" t="s">
+        <v>126</v>
+      </c>
+      <c r="E159">
+        <v>0.4722</v>
+      </c>
+      <c r="F159" t="b">
         <v>1</v>
       </c>
     </row>

--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="146">
   <si>
     <t>process_hash</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>d9bbe9c16b24a1ef</t>
+  </si>
+  <si>
+    <t>5de8abf098149c95</t>
+  </si>
+  <si>
+    <t>f7c601315446df1a</t>
+  </si>
+  <si>
+    <t>d153751413d830ba</t>
   </si>
   <si>
     <t>synthetic-compliance-rules-#1</t>
@@ -804,7 +813,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -832,13 +841,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -852,13 +861,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -872,13 +881,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -892,13 +901,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -912,13 +921,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -932,13 +941,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -952,13 +961,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -972,13 +981,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -992,13 +1001,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -1012,13 +1021,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -1032,13 +1041,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -1052,13 +1061,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C13">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -1072,13 +1081,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -1092,13 +1101,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -1112,13 +1121,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -1132,13 +1141,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -1152,13 +1161,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -1172,13 +1181,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -1192,13 +1201,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -1212,13 +1221,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
@@ -1232,13 +1241,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E22">
         <v>0.6777</v>
@@ -1252,13 +1261,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E23">
         <v>0.6778999999999999</v>
@@ -1272,13 +1281,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E24">
         <v>0.6841</v>
@@ -1292,13 +1301,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>0.6841</v>
@@ -1312,13 +1321,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>0.6841</v>
@@ -1332,13 +1341,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E27">
         <v>0.6841</v>
@@ -1352,13 +1361,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E28">
         <v>0.5894</v>
@@ -1372,13 +1381,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>0.6067</v>
@@ -1392,13 +1401,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E30">
         <v>0.6036</v>
@@ -1412,13 +1421,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E31">
         <v>0.6428</v>
@@ -1432,13 +1441,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E32">
         <v>0.4052</v>
@@ -1452,13 +1461,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E33">
         <v>0.625</v>
@@ -1472,13 +1481,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E34">
         <v>0.6039</v>
@@ -1492,13 +1501,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E35">
         <v>0.6194</v>
@@ -1512,13 +1521,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E36">
         <v>0.6367</v>
@@ -1532,13 +1541,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E37">
         <v>0.6216</v>
@@ -1552,13 +1561,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E38">
         <v>0.6395999999999999</v>
@@ -1572,13 +1581,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E39">
         <v>0.6151</v>
@@ -1592,13 +1601,13 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E40">
         <v>0.6411</v>
@@ -1612,13 +1621,13 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E41">
         <v>0.4462</v>
@@ -1632,13 +1641,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E42">
         <v>0.5122</v>
@@ -1652,13 +1661,13 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E43">
         <v>0.5894</v>
@@ -1672,13 +1681,13 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E44">
         <v>0.6067</v>
@@ -1692,13 +1701,13 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E45">
         <v>0.6036</v>
@@ -1712,13 +1721,13 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E46">
         <v>0.6428</v>
@@ -1732,13 +1741,13 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E47">
         <v>0.4052</v>
@@ -1752,13 +1761,13 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C48">
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E48">
         <v>0.625</v>
@@ -1772,13 +1781,13 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E49">
         <v>0.6039</v>
@@ -1792,13 +1801,13 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E50">
         <v>0.4927</v>
@@ -1812,13 +1821,13 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E51">
         <v>0.6346000000000001</v>
@@ -1832,13 +1841,13 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E52">
         <v>0.3461</v>
@@ -1852,13 +1861,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E53">
         <v>0.15</v>
@@ -1872,13 +1881,13 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E54">
         <v>0.4212</v>
@@ -1892,13 +1901,13 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C55">
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E55">
         <v>0.3107</v>
@@ -1912,13 +1921,13 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C56">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E56">
         <v>0.2965</v>
@@ -1932,13 +1941,13 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C57">
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E57">
         <v>0.2812</v>
@@ -1952,13 +1961,13 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C58">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E58">
         <v>0.2349</v>
@@ -1972,13 +1981,13 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C59">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E59">
         <v>0.6031</v>
@@ -1992,13 +2001,13 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C60">
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E60">
         <v>0.4668</v>
@@ -2012,13 +2021,13 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E61">
         <v>0.4043</v>
@@ -2032,13 +2041,13 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E62">
         <v>0.496</v>
@@ -2052,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E63">
         <v>0.4781</v>
@@ -2072,13 +2081,13 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C64">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E64">
         <v>0.5125</v>
@@ -2092,13 +2101,13 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C65">
         <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E65">
         <v>0.3548</v>
@@ -2112,13 +2121,13 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C66">
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E66">
         <v>0.2212</v>
@@ -2132,13 +2141,13 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C67">
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E67">
         <v>0.3205</v>
@@ -2152,13 +2161,13 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C68">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E68">
         <v>0.2504</v>
@@ -2172,13 +2181,13 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C69">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E69">
         <v>0.51</v>
@@ -2192,13 +2201,13 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C70">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E70">
         <v>0.4057</v>
@@ -2212,13 +2221,13 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E71">
         <v>0.6163999999999999</v>
@@ -2232,13 +2241,13 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E72">
         <v>0.5685</v>
@@ -2252,13 +2261,13 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E73">
         <v>0.6151</v>
@@ -2272,13 +2281,13 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C74">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E74">
         <v>0.6232</v>
@@ -2292,13 +2301,13 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C75">
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E75">
         <v>0.5322</v>
@@ -2312,13 +2321,13 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C76">
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E76">
         <v>0.3512</v>
@@ -2332,13 +2341,13 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C77">
         <v>7</v>
       </c>
       <c r="D77" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E77">
         <v>0.4761</v>
@@ -2352,13 +2361,13 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C78">
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E78">
         <v>0.481</v>
@@ -2372,13 +2381,13 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C79">
         <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E79">
         <v>0.5723</v>
@@ -2392,13 +2401,13 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C80">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E80">
         <v>0.6477000000000001</v>
@@ -2412,13 +2421,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E81">
         <v>0.4285</v>
@@ -2432,13 +2441,13 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E82">
         <v>0.5831</v>
@@ -2452,13 +2461,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E83">
         <v>0.3756</v>
@@ -2472,13 +2481,13 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C84">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E84">
         <v>0.4707</v>
@@ -2492,13 +2501,13 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C85">
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E85">
         <v>0.4945</v>
@@ -2512,13 +2521,13 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C86">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E86">
         <v>0.3551</v>
@@ -2532,13 +2541,13 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C87">
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E87">
         <v>0.5426</v>
@@ -2552,13 +2561,13 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C88">
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E88">
         <v>0.5185999999999999</v>
@@ -2572,13 +2581,13 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C89">
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E89">
         <v>0.3634</v>
@@ -2592,13 +2601,13 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C90">
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E90">
         <v>0.4161</v>
@@ -2612,13 +2621,13 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C91">
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E91">
         <v>0.2871</v>
@@ -2632,13 +2641,13 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C92">
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E92">
         <v>0.506</v>
@@ -2652,13 +2661,13 @@
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C93">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E93">
         <v>0.4668</v>
@@ -2672,13 +2681,13 @@
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C94">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E94">
         <v>0.3633</v>
@@ -2692,13 +2701,13 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C95">
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E95">
         <v>0.3922</v>
@@ -2712,13 +2721,13 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C96">
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E96">
         <v>0.4302</v>
@@ -2732,13 +2741,13 @@
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C97">
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E97">
         <v>0.4779</v>
@@ -2752,13 +2761,13 @@
         <v>10</v>
       </c>
       <c r="B98" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C98">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E98">
         <v>0.4652</v>
@@ -2772,13 +2781,13 @@
         <v>10</v>
       </c>
       <c r="B99" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C99">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E99">
         <v>0.4672</v>
@@ -2792,13 +2801,13 @@
         <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C100">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E100">
         <v>0.4137</v>
@@ -2812,13 +2821,13 @@
         <v>10</v>
       </c>
       <c r="B101" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C101">
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E101">
         <v>0.3759</v>
@@ -2832,13 +2841,13 @@
         <v>10</v>
       </c>
       <c r="B102" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C102">
         <v>22</v>
       </c>
       <c r="D102" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E102">
         <v>0.3841</v>
@@ -2852,13 +2861,13 @@
         <v>10</v>
       </c>
       <c r="B103" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C103">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E103">
         <v>0.377</v>
@@ -2872,13 +2881,13 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E104">
         <v>0.589</v>
@@ -2892,13 +2901,13 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E105">
         <v>0.5769</v>
@@ -2912,13 +2921,13 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E106">
         <v>0.8023</v>
@@ -2932,13 +2941,13 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C107">
         <v>4</v>
       </c>
       <c r="D107" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E107">
         <v>0.6107</v>
@@ -2952,13 +2961,13 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C108">
         <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E108">
         <v>0.5578</v>
@@ -2972,13 +2981,13 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C109">
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E109">
         <v>0.525</v>
@@ -2992,13 +3001,13 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E110">
         <v>0.6331</v>
@@ -3012,13 +3021,13 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E111">
         <v>0.6157</v>
@@ -3032,13 +3041,13 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C112">
         <v>4</v>
       </c>
       <c r="D112" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E112">
         <v>0.5907</v>
@@ -3052,13 +3061,13 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C113">
         <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E113">
         <v>0.5887</v>
@@ -3072,13 +3081,13 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E114">
         <v>0.4681</v>
@@ -3092,13 +3101,13 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E115">
         <v>0.5196</v>
@@ -3112,13 +3121,13 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E116">
         <v>0.4807</v>
@@ -3132,13 +3141,13 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C117">
         <v>4</v>
       </c>
       <c r="D117" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E117">
         <v>0.5272</v>
@@ -3152,13 +3161,13 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C118">
         <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E118">
         <v>0.4035</v>
@@ -3172,13 +3181,13 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C119">
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E119">
         <v>0.2197</v>
@@ -3192,13 +3201,13 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C120">
         <v>7</v>
       </c>
       <c r="D120" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E120">
         <v>0.3409</v>
@@ -3212,13 +3221,13 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C121">
         <v>8</v>
       </c>
       <c r="D121" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E121">
         <v>0.306</v>
@@ -3232,13 +3241,13 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C122">
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E122">
         <v>0.5057</v>
@@ -3252,13 +3261,13 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C123">
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E123">
         <v>0.391</v>
@@ -3272,13 +3281,13 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C124">
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E124">
         <v>0.4744</v>
@@ -3292,13 +3301,13 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E125">
         <v>0.5164</v>
@@ -3312,13 +3321,13 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C126">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E126">
         <v>0.4936</v>
@@ -3332,13 +3341,13 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C127">
         <v>4</v>
       </c>
       <c r="D127" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E127">
         <v>0.5272</v>
@@ -3352,13 +3361,13 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C128">
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E128">
         <v>0.3482</v>
@@ -3372,13 +3381,13 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C129">
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E129">
         <v>0.2297</v>
@@ -3392,13 +3401,13 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C130">
         <v>7</v>
       </c>
       <c r="D130" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E130">
         <v>0.3378</v>
@@ -3412,13 +3421,13 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C131">
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E131">
         <v>0.3239</v>
@@ -3432,13 +3441,13 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C132">
         <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E132">
         <v>0.5134</v>
@@ -3452,13 +3461,13 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C133">
         <v>10</v>
       </c>
       <c r="D133" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E133">
         <v>0.4012</v>
@@ -3472,13 +3481,13 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E134">
         <v>0.4637</v>
@@ -3492,13 +3501,13 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C135">
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E135">
         <v>0.5274</v>
@@ -3512,13 +3521,13 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C136">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="E136">
         <v>0.466</v>
@@ -3532,13 +3541,13 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C137">
         <v>4</v>
       </c>
       <c r="D137" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E137">
         <v>0.4992</v>
@@ -3552,13 +3561,13 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C138">
         <v>5</v>
       </c>
       <c r="D138" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E138">
         <v>0.3147</v>
@@ -3572,13 +3581,13 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C139">
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E139">
         <v>0.2325</v>
@@ -3592,13 +3601,13 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C140">
         <v>7</v>
       </c>
       <c r="D140" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E140">
         <v>0.3077</v>
@@ -3612,13 +3621,13 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C141">
         <v>8</v>
       </c>
       <c r="D141" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E141">
         <v>0.3327</v>
@@ -3632,13 +3641,13 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C142">
         <v>9</v>
       </c>
       <c r="D142" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E142">
         <v>0.5164</v>
@@ -3652,13 +3661,13 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C143">
         <v>10</v>
       </c>
       <c r="D143" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E143">
         <v>0.4241</v>
@@ -3672,13 +3681,13 @@
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E144">
         <v>0.5915</v>
@@ -3692,13 +3701,13 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E145">
         <v>0.594</v>
@@ -3712,13 +3721,13 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C146">
         <v>3</v>
       </c>
       <c r="D146" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E146">
         <v>0.6373</v>
@@ -3732,13 +3741,13 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C147">
         <v>4</v>
       </c>
       <c r="D147" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E147">
         <v>0.7056</v>
@@ -3752,13 +3761,13 @@
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C148">
         <v>5</v>
       </c>
       <c r="D148" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E148">
         <v>0.6233</v>
@@ -3772,13 +3781,13 @@
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C149">
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E149">
         <v>0.5113</v>
@@ -3792,13 +3801,13 @@
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C150">
         <v>7</v>
       </c>
       <c r="D150" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E150">
         <v>0.3871</v>
@@ -3812,13 +3821,13 @@
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C151">
         <v>8</v>
       </c>
       <c r="D151" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E151">
         <v>0.375</v>
@@ -3832,13 +3841,13 @@
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C152">
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E152">
         <v>0.4379</v>
@@ -3852,13 +3861,13 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C153">
         <v>10</v>
       </c>
       <c r="D153" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E153">
         <v>0.5532</v>
@@ -3872,13 +3881,13 @@
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C154">
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E154">
         <v>0.3674</v>
@@ -3892,13 +3901,13 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>32</v>
-      </c>
-      <c r="C155" t="s">
         <v>35</v>
       </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
       <c r="D155" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E155">
         <v>0.5351</v>
@@ -3912,13 +3921,13 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>32</v>
-      </c>
-      <c r="C156" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="C156">
+        <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E156">
         <v>0.5658</v>
@@ -3932,13 +3941,13 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>32</v>
-      </c>
-      <c r="C157" t="s">
-        <v>37</v>
+        <v>35</v>
+      </c>
+      <c r="C157">
+        <v>3</v>
       </c>
       <c r="D157" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E157">
         <v>0.8372000000000001</v>
@@ -3952,13 +3961,13 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>32</v>
-      </c>
-      <c r="C158" t="s">
-        <v>38</v>
+        <v>35</v>
+      </c>
+      <c r="C158">
+        <v>4</v>
       </c>
       <c r="D158" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E158">
         <v>0.6856</v>
@@ -3972,18 +3981,318 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>32</v>
-      </c>
-      <c r="C159" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="C159">
+        <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E159">
         <v>0.4722</v>
       </c>
       <c r="F159" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" t="s">
+        <v>17</v>
+      </c>
+      <c r="B160" t="s">
+        <v>35</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160" t="s">
+        <v>125</v>
+      </c>
+      <c r="E160">
+        <v>0.5958</v>
+      </c>
+      <c r="F160" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
+      <c r="A161" t="s">
+        <v>17</v>
+      </c>
+      <c r="B161" t="s">
+        <v>35</v>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+      <c r="D161" t="s">
+        <v>126</v>
+      </c>
+      <c r="E161">
+        <v>0.5648</v>
+      </c>
+      <c r="F161" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
+      <c r="A162" t="s">
+        <v>17</v>
+      </c>
+      <c r="B162" t="s">
+        <v>35</v>
+      </c>
+      <c r="C162">
+        <v>3</v>
+      </c>
+      <c r="D162" t="s">
+        <v>127</v>
+      </c>
+      <c r="E162">
+        <v>0.8122</v>
+      </c>
+      <c r="F162" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
+      <c r="A163" t="s">
+        <v>17</v>
+      </c>
+      <c r="B163" t="s">
+        <v>35</v>
+      </c>
+      <c r="C163">
+        <v>4</v>
+      </c>
+      <c r="D163" t="s">
+        <v>128</v>
+      </c>
+      <c r="E163">
+        <v>0.5341</v>
+      </c>
+      <c r="F163" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
+      <c r="A164" t="s">
+        <v>17</v>
+      </c>
+      <c r="B164" t="s">
+        <v>35</v>
+      </c>
+      <c r="C164">
+        <v>5</v>
+      </c>
+      <c r="D164" t="s">
+        <v>129</v>
+      </c>
+      <c r="E164">
+        <v>0.4946</v>
+      </c>
+      <c r="F164" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="A165" t="s">
+        <v>18</v>
+      </c>
+      <c r="B165" t="s">
+        <v>35</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165" t="s">
+        <v>125</v>
+      </c>
+      <c r="E165">
+        <v>0.45</v>
+      </c>
+      <c r="F165" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
+      <c r="A166" t="s">
+        <v>18</v>
+      </c>
+      <c r="B166" t="s">
+        <v>35</v>
+      </c>
+      <c r="C166">
+        <v>2</v>
+      </c>
+      <c r="D166" t="s">
+        <v>126</v>
+      </c>
+      <c r="E166">
+        <v>0.4242</v>
+      </c>
+      <c r="F166" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
+      <c r="A167" t="s">
+        <v>18</v>
+      </c>
+      <c r="B167" t="s">
+        <v>35</v>
+      </c>
+      <c r="C167">
+        <v>3</v>
+      </c>
+      <c r="D167" t="s">
+        <v>127</v>
+      </c>
+      <c r="E167">
+        <v>0.6752</v>
+      </c>
+      <c r="F167" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
+      <c r="A168" t="s">
+        <v>18</v>
+      </c>
+      <c r="B168" t="s">
+        <v>35</v>
+      </c>
+      <c r="C168">
+        <v>4</v>
+      </c>
+      <c r="D168" t="s">
+        <v>128</v>
+      </c>
+      <c r="E168">
+        <v>0.4821</v>
+      </c>
+      <c r="F168" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
+      <c r="A169" t="s">
+        <v>18</v>
+      </c>
+      <c r="B169" t="s">
+        <v>35</v>
+      </c>
+      <c r="C169">
+        <v>5</v>
+      </c>
+      <c r="D169" t="s">
+        <v>129</v>
+      </c>
+      <c r="E169">
+        <v>0.4399</v>
+      </c>
+      <c r="F169" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
+      <c r="A170" t="s">
+        <v>19</v>
+      </c>
+      <c r="B170" t="s">
+        <v>35</v>
+      </c>
+      <c r="C170" t="s">
+        <v>38</v>
+      </c>
+      <c r="D170" t="s">
+        <v>125</v>
+      </c>
+      <c r="E170">
+        <v>0.5006</v>
+      </c>
+      <c r="F170" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
+      <c r="A171" t="s">
+        <v>19</v>
+      </c>
+      <c r="B171" t="s">
+        <v>35</v>
+      </c>
+      <c r="C171" t="s">
+        <v>39</v>
+      </c>
+      <c r="D171" t="s">
+        <v>126</v>
+      </c>
+      <c r="E171">
+        <v>0.5268</v>
+      </c>
+      <c r="F171" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
+      <c r="A172" t="s">
+        <v>19</v>
+      </c>
+      <c r="B172" t="s">
+        <v>35</v>
+      </c>
+      <c r="C172" t="s">
+        <v>40</v>
+      </c>
+      <c r="D172" t="s">
+        <v>127</v>
+      </c>
+      <c r="E172">
+        <v>0.8122</v>
+      </c>
+      <c r="F172" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
+      <c r="A173" t="s">
+        <v>19</v>
+      </c>
+      <c r="B173" t="s">
+        <v>35</v>
+      </c>
+      <c r="C173" t="s">
+        <v>41</v>
+      </c>
+      <c r="D173" t="s">
+        <v>128</v>
+      </c>
+      <c r="E173">
+        <v>0.5647</v>
+      </c>
+      <c r="F173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="A174" t="s">
+        <v>19</v>
+      </c>
+      <c r="B174" t="s">
+        <v>35</v>
+      </c>
+      <c r="C174" t="s">
+        <v>42</v>
+      </c>
+      <c r="D174" t="s">
+        <v>129</v>
+      </c>
+      <c r="E174">
+        <v>0.4946</v>
+      </c>
+      <c r="F174" t="b">
         <v>1</v>
       </c>
     </row>

--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="201">
   <si>
     <t>process_hash</t>
   </si>
@@ -76,6 +76,15 @@
     <t>d153751413d830ba</t>
   </si>
   <si>
+    <t>c8736219f33e790f</t>
+  </si>
+  <si>
+    <t>98e721e49a3373e4</t>
+  </si>
+  <si>
+    <t>b4d05022165f08ab</t>
+  </si>
+  <si>
     <t>synthetic-compliance-rules-#1</t>
   </si>
   <si>
@@ -130,6 +139,12 @@
     <t>claude_merchant_onboarding</t>
   </si>
   <si>
+    <t>ki</t>
+  </si>
+  <si>
+    <t>ki2</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -143,6 +158,63 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
@@ -482,6 +554,115 @@
   </si>
   <si>
     <t>21Consumer complaints must be acknowledged within two business days and resolved within 30 calendar days of receipt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Datenschutz-Richtlinie_Kunstliche_Intelligenz_KI-070426-133246.pdf
+Richtlinie Künstliche Intelligenz (KI) Vorgaben und Nutzungshinweise für den Einsatz von KI / ML-Systemen mit der Beschreibung der </t>
+  </si>
+  <si>
+    <t>1    Einleitung Bei der viadee kann der Bedarf bestehen, Angebote von Künstlicher Intelligenz (KI) zu nutzen .
+Damit sind KI-Systeme im Sinne des EU Ai Acts gemeint ( ), insb. Dienste im Internet.
+Bei</t>
+  </si>
+  <si>
+    <t>1. “KI-Tools dürfen nicht allein und ohne menschliche Überprüfung, sondern ausschließlich unterstützend eingesetzt werden, wenn es um die Bewertung oder Beurteilung von Menschen geht.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. KI-Systeme sollen nicht mit viadee internen Informationen versorgt werden, insbesondere gilt dies für sicherheitsrelevante Informationen und für personenbezogenen Daten wenn sie im Sinne der DSGVO </t>
+  </si>
+  <si>
+    <t>3. KI-generierte Ergebnisse sollten kritisch geprüft und hinterfragt und nicht unbesehen verwendet sowie nötigenfalls gekennzeichnet werden.</t>
+  </si>
+  <si>
+    <t>4. Die viadee stellt geprüfte KI-Tools und Dienste zur Verfügung - nur diese sind zu verwenden.
+Ausnahmen zu Test- und Analysenzwecken sind nach Rücksprache mit Verantwortlichen und gegebenenfalls Bet</t>
+  </si>
+  <si>
+    <t>2    Geltungsbereich Diese Richtlinie verpflichtet alle Beschäftigten der viadee zur Einhaltung der hier festgelegten Vorgaben im Umgang mit KI- Systemen, während sie für die viadee agieren.
+Sollte im</t>
+  </si>
+  <si>
+    <t>3    Zulässigkeit des Einsatzes von KI / ML- Systemen</t>
+  </si>
+  <si>
+    <t>1. Nutzbare Software: Nur freigegebene KI-Systeme dürfen verwendet werden. Diese sind auf der Liste der explizit aufgeführt.
+Deren grundsätzliche Verwendbarkeit inklusive deren KI- Funktionen wird aus</t>
+  </si>
+  <si>
+    <t>2. Bei der Benutzung sind die dort genannten Nutzungskonzepte zu beachten.</t>
+  </si>
+  <si>
+    <t>3. Es dürfen darüber hinaus keine KI-Systeme verwendet werden, die die Eingaben von Anwender:innen, ggf.
+mitgesendete Kontextinformationen sowie die Ausgaben des KI-Systems zum Training verwenden.
+Ein</t>
+  </si>
+  <si>
+    <t>4    Verwendungseinschränkung von KI / ML- Systemen</t>
+  </si>
+  <si>
+    <t>1. Die Verwendung von a. als geheimhaltungsbedürftig eingestuften Informationen (z.B. Geschäfts- und Betriebsgeheimnisse oder sonstige Informationen, die einen besonderen wirtschaftlichen Wert für via</t>
+  </si>
+  <si>
+    <t>2. Die Nutzung eines KI-Systems zum Zweck der Erstellung von Beurteilungen der Persönlichkeit, der Arbeitsleistung, der physischen und psychischen Belastbarkeit, der kognitiven oder emotionalen Fähigk</t>
+  </si>
+  <si>
+    <t>3. Die jeweiligen KI-Tool Bedingungen sind zu beachten. Typischerweise sind diese in AGB, “Terms of Use”, “Acceptable Use” oder vergleichbaren Dokumenten zu finden.</t>
+  </si>
+  <si>
+    <t>5    Verantwortungsvoller Umgang mit KI-generierten Ergebnissen</t>
+  </si>
+  <si>
+    <t>1. Transparenz a. Wenn wir KI-Systeme betreiben, stellen wir sicher, dass sie als solche zu erkennen sind (Vgl.
+).
+b. Werden die Ergebnisse eines KI-Systems ganz oder teilweise veröffentlicht oder für</t>
+  </si>
+  <si>
+    <t>2. Da auf rein generierten Inhalten kein Urheberrecht entsteht, sind alle Inhalte manuell nachzubearbeiten, für die die viadee eine Urheberschaft anstrebt.</t>
+  </si>
+  <si>
+    <t>3. Der Dienst kann ungenaue oder falsche Informationen erstellen. Daher sind die Beschäftigten der viadee verpflichtet, die fachliche und sachliche Korrektheit der erstellten Ergebnisse durch ihr Expe</t>
+  </si>
+  <si>
+    <t>4. Ungeprüfte Arbeitsergebnisse eines KI-Tools müssen in der Kommunikation immer als solche gekennzeichnet werden.</t>
+  </si>
+  <si>
+    <t>5. Ein KI-Tool kann Ergebnisse liefern, die unter Umständen bereits urheberrechtlich geschützten Werken entsprechen. Bei Verdachtsfällen und wenn wir nicht durch den Anbieter der Software von Urheberr</t>
+  </si>
+  <si>
+    <t>6. Ein KI-Tool kann Ergebnisse liefern, die z. B. das Markenrecht, das Recht auf das eigene Bild, Verbot von Diskriminierung oder andere Gesetze zu den Ergebnistypen (Text, Bild, Audio, …) einer KI ve</t>
+  </si>
+  <si>
+    <t>6    Zum Umgang mit dieser Richtlinie Im Zweifel oder bei Unsicherheiten bei dem Einsatz eines KI-Tools oder Dienstes oder im Umgang mit den Vorgaben und Empfehlungen dieser Richtlinie sollte Rückspra</t>
+  </si>
+  <si>
+    <t>7    Aktualisierung dieser Richtlinie Die Gesetzgebung zum Thema KI hat eine hohe Dynamik und diese kann sich auf die Inhalte dieser Richtlinie auswirken. Weiterhin können z. B. neue Möglichkeiten der</t>
+  </si>
+  <si>
+    <t>1    Einleitung Bei der viadee kann der Bedarf bestehen, Angebote von Künstlicher Intelligenz (KI) zu nutzen .
+Damit sind KI-Systeme im Sinne des EU Ai Acts gemeint (hier erklärt), insb. Dienste im In</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2    Geltungsbereich Diese Richtlinie verpflichtet alle Beschäftigten der viadee zur Einhaltung der hier festgelegten Vorgaben im Umgang mit KI-Systemen, während sie für die viadee agieren.
+Sollte im </t>
+  </si>
+  <si>
+    <t>3    Zulässigkeit des Einsatzes von KI / ML-Systemen Nutzbare Software: Nur freigegebene KI-Systeme dürfen verwendet werden. Diese sind auf der Liste der KI-Anwendungen explizit aufgeführt.
+Deren grun</t>
+  </si>
+  <si>
+    <t>4    Verwendungseinschränkung von KI / ML-Systemen Die Verwendung von
+als geheimhaltungsbedürftigVerpflichtungserklärung Daten- und Geschäftsgeheimnis (Wiki-Version)eingestuften Informationen (z.B. Ge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5    Verantwortungsvoller Umgang mit KI-generierten Ergebnissen Transparenz
+Wenn wir KI-Systeme betreiben, stellen wir sicher, dass sie als solche zu erkennen sind (Vgl. EU Ai Act Artikel 50).
+Werden </t>
+  </si>
+  <si>
+    <t>6    Zum Umgang mit dieser Richtlinie Im Zweifel oder bei Unsicherheiten bei dem Einsatz eines KI-Tools oder Dienstes oder im Umgang mit den Vorgaben und Empfehlungen dieser Richtlinie sollte Rückspra</t>
+  </si>
+  <si>
+    <t>7    Aktualisierung dieser Richtlinie Die Gesetzgebung zum Thema KI hat eine hohe Dynamik und diese kann sich auf die Inhalte dieser Richtlinie auswirken. Weiterhin können z. B. neue Möglichkeiten der</t>
   </si>
 </sst>
 </file>
@@ -813,7 +994,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -841,13 +1022,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -861,13 +1042,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -881,13 +1062,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -901,13 +1082,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -921,13 +1102,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -941,13 +1122,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -961,13 +1142,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -981,13 +1162,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -1001,13 +1182,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -1021,13 +1202,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -1041,13 +1222,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -1061,13 +1242,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C13">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -1081,13 +1262,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -1101,13 +1282,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -1121,13 +1302,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C16">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -1141,13 +1322,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C17">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -1161,13 +1342,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -1181,13 +1362,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -1201,13 +1382,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -1221,13 +1402,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
@@ -1241,13 +1422,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="E22">
         <v>0.6777</v>
@@ -1261,13 +1442,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="E23">
         <v>0.6778999999999999</v>
@@ -1281,13 +1462,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="E24">
         <v>0.6841</v>
@@ -1301,13 +1482,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E25">
         <v>0.6841</v>
@@ -1321,13 +1502,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E26">
         <v>0.6841</v>
@@ -1341,13 +1522,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E27">
         <v>0.6841</v>
@@ -1361,13 +1542,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E28">
         <v>0.5894</v>
@@ -1381,13 +1562,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E29">
         <v>0.6067</v>
@@ -1401,13 +1582,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E30">
         <v>0.6036</v>
@@ -1421,13 +1602,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E31">
         <v>0.6428</v>
@@ -1441,13 +1622,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="E32">
         <v>0.4052</v>
@@ -1461,13 +1642,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E33">
         <v>0.625</v>
@@ -1481,13 +1662,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E34">
         <v>0.6039</v>
@@ -1501,13 +1682,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E35">
         <v>0.6194</v>
@@ -1521,13 +1702,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>0.6367</v>
@@ -1541,13 +1722,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="E37">
         <v>0.6216</v>
@@ -1561,13 +1742,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>0.6395999999999999</v>
@@ -1581,13 +1762,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="E39">
         <v>0.6151</v>
@@ -1601,13 +1782,13 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="E40">
         <v>0.6411</v>
@@ -1621,13 +1802,13 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E41">
         <v>0.4462</v>
@@ -1641,13 +1822,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E42">
         <v>0.5122</v>
@@ -1661,13 +1842,13 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="E43">
         <v>0.5894</v>
@@ -1681,13 +1862,13 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E44">
         <v>0.6067</v>
@@ -1701,13 +1882,13 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E45">
         <v>0.6036</v>
@@ -1721,13 +1902,13 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E46">
         <v>0.6428</v>
@@ -1741,13 +1922,13 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="E47">
         <v>0.4052</v>
@@ -1761,13 +1942,13 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C48">
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="E48">
         <v>0.625</v>
@@ -1781,13 +1962,13 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E49">
         <v>0.6039</v>
@@ -1801,13 +1982,13 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>81</v>
+        <v>105</v>
       </c>
       <c r="E50">
         <v>0.4927</v>
@@ -1821,13 +2002,13 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E51">
         <v>0.6346000000000001</v>
@@ -1841,13 +2022,13 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>83</v>
+        <v>107</v>
       </c>
       <c r="E52">
         <v>0.3461</v>
@@ -1861,13 +2042,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="E53">
         <v>0.15</v>
@@ -1881,13 +2062,13 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="E54">
         <v>0.4212</v>
@@ -1901,13 +2082,13 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C55">
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>86</v>
+        <v>110</v>
       </c>
       <c r="E55">
         <v>0.3107</v>
@@ -1921,13 +2102,13 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C56">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="E56">
         <v>0.2965</v>
@@ -1941,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C57">
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="E57">
         <v>0.2812</v>
@@ -1961,13 +2142,13 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C58">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="E58">
         <v>0.2349</v>
@@ -1981,13 +2162,13 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C59">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E59">
         <v>0.6031</v>
@@ -2001,13 +2182,13 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C60">
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E60">
         <v>0.4668</v>
@@ -2021,13 +2202,13 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E61">
         <v>0.4043</v>
@@ -2041,13 +2222,13 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E62">
         <v>0.496</v>
@@ -2061,13 +2242,13 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E63">
         <v>0.4781</v>
@@ -2081,13 +2262,13 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C64">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E64">
         <v>0.5125</v>
@@ -2101,13 +2282,13 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C65">
         <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E65">
         <v>0.3548</v>
@@ -2121,13 +2302,13 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C66">
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E66">
         <v>0.2212</v>
@@ -2141,13 +2322,13 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C67">
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E67">
         <v>0.3205</v>
@@ -2161,13 +2342,13 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C68">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E68">
         <v>0.2504</v>
@@ -2181,13 +2362,13 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C69">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E69">
         <v>0.51</v>
@@ -2201,13 +2382,13 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C70">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E70">
         <v>0.4057</v>
@@ -2221,13 +2402,13 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E71">
         <v>0.6163999999999999</v>
@@ -2241,13 +2422,13 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E72">
         <v>0.5685</v>
@@ -2261,13 +2442,13 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E73">
         <v>0.6151</v>
@@ -2281,13 +2462,13 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C74">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E74">
         <v>0.6232</v>
@@ -2301,13 +2482,13 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C75">
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E75">
         <v>0.5322</v>
@@ -2321,13 +2502,13 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C76">
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E76">
         <v>0.3512</v>
@@ -2341,13 +2522,13 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C77">
         <v>7</v>
       </c>
       <c r="D77" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E77">
         <v>0.4761</v>
@@ -2361,13 +2542,13 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C78">
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E78">
         <v>0.481</v>
@@ -2381,13 +2562,13 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C79">
         <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E79">
         <v>0.5723</v>
@@ -2401,13 +2582,13 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C80">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E80">
         <v>0.6477000000000001</v>
@@ -2421,13 +2602,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="E81">
         <v>0.4285</v>
@@ -2441,13 +2622,13 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="E82">
         <v>0.5831</v>
@@ -2461,13 +2642,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="E83">
         <v>0.3756</v>
@@ -2481,13 +2662,13 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C84">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="E84">
         <v>0.4707</v>
@@ -2501,13 +2682,13 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C85">
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="E85">
         <v>0.4945</v>
@@ -2521,13 +2702,13 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C86">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="E86">
         <v>0.3551</v>
@@ -2541,13 +2722,13 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C87">
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="E87">
         <v>0.5426</v>
@@ -2561,13 +2742,13 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C88">
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="E88">
         <v>0.5185999999999999</v>
@@ -2581,13 +2762,13 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C89">
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E89">
         <v>0.3634</v>
@@ -2601,13 +2782,13 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C90">
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="E90">
         <v>0.4161</v>
@@ -2621,13 +2802,13 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C91">
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E91">
         <v>0.2871</v>
@@ -2641,13 +2822,13 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C92">
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="E92">
         <v>0.506</v>
@@ -2661,13 +2842,13 @@
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C93">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="E93">
         <v>0.4668</v>
@@ -2681,13 +2862,13 @@
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C94">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="E94">
         <v>0.3633</v>
@@ -2701,13 +2882,13 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C95">
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="E95">
         <v>0.3922</v>
@@ -2721,13 +2902,13 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C96">
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="E96">
         <v>0.4302</v>
@@ -2741,13 +2922,13 @@
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C97">
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="E97">
         <v>0.4779</v>
@@ -2761,13 +2942,13 @@
         <v>10</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C98">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="E98">
         <v>0.4652</v>
@@ -2781,13 +2962,13 @@
         <v>10</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C99">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="E99">
         <v>0.4672</v>
@@ -2801,13 +2982,13 @@
         <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C100">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="E100">
         <v>0.4137</v>
@@ -2821,13 +3002,13 @@
         <v>10</v>
       </c>
       <c r="B101" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C101">
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="E101">
         <v>0.3759</v>
@@ -2841,13 +3022,13 @@
         <v>10</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C102">
         <v>22</v>
       </c>
       <c r="D102" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="E102">
         <v>0.3841</v>
@@ -2861,13 +3042,13 @@
         <v>10</v>
       </c>
       <c r="B103" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C103">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="E103">
         <v>0.377</v>
@@ -2881,13 +3062,13 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E104">
         <v>0.589</v>
@@ -2901,13 +3082,13 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E105">
         <v>0.5769</v>
@@ -2921,13 +3102,13 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E106">
         <v>0.8023</v>
@@ -2941,13 +3122,13 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C107">
         <v>4</v>
       </c>
       <c r="D107" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E107">
         <v>0.6107</v>
@@ -2961,13 +3142,13 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C108">
         <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E108">
         <v>0.5578</v>
@@ -2981,13 +3162,13 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C109">
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>130</v>
+        <v>154</v>
       </c>
       <c r="E109">
         <v>0.525</v>
@@ -3001,13 +3182,13 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>131</v>
+        <v>155</v>
       </c>
       <c r="E110">
         <v>0.6331</v>
@@ -3021,13 +3202,13 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="E111">
         <v>0.6157</v>
@@ -3041,13 +3222,13 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C112">
         <v>4</v>
       </c>
       <c r="D112" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="E112">
         <v>0.5907</v>
@@ -3061,13 +3242,13 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C113">
         <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="E113">
         <v>0.5887</v>
@@ -3081,13 +3262,13 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E114">
         <v>0.4681</v>
@@ -3101,13 +3282,13 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E115">
         <v>0.5196</v>
@@ -3121,13 +3302,13 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E116">
         <v>0.4807</v>
@@ -3141,13 +3322,13 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C117">
         <v>4</v>
       </c>
       <c r="D117" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E117">
         <v>0.5272</v>
@@ -3161,13 +3342,13 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C118">
         <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E118">
         <v>0.4035</v>
@@ -3181,13 +3362,13 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C119">
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E119">
         <v>0.2197</v>
@@ -3201,13 +3382,13 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C120">
         <v>7</v>
       </c>
       <c r="D120" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E120">
         <v>0.3409</v>
@@ -3221,13 +3402,13 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C121">
         <v>8</v>
       </c>
       <c r="D121" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E121">
         <v>0.306</v>
@@ -3241,13 +3422,13 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C122">
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E122">
         <v>0.5057</v>
@@ -3261,13 +3442,13 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C123">
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E123">
         <v>0.391</v>
@@ -3281,13 +3462,13 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C124">
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E124">
         <v>0.4744</v>
@@ -3301,13 +3482,13 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E125">
         <v>0.5164</v>
@@ -3321,13 +3502,13 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C126">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E126">
         <v>0.4936</v>
@@ -3341,13 +3522,13 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C127">
         <v>4</v>
       </c>
       <c r="D127" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E127">
         <v>0.5272</v>
@@ -3361,13 +3542,13 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C128">
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E128">
         <v>0.3482</v>
@@ -3381,13 +3562,13 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C129">
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E129">
         <v>0.2297</v>
@@ -3401,13 +3582,13 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C130">
         <v>7</v>
       </c>
       <c r="D130" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E130">
         <v>0.3378</v>
@@ -3421,13 +3602,13 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C131">
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E131">
         <v>0.3239</v>
@@ -3441,13 +3622,13 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C132">
         <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E132">
         <v>0.5134</v>
@@ -3461,13 +3642,13 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C133">
         <v>10</v>
       </c>
       <c r="D133" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E133">
         <v>0.4012</v>
@@ -3481,13 +3662,13 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="E134">
         <v>0.4637</v>
@@ -3501,13 +3682,13 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C135">
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="E135">
         <v>0.5274</v>
@@ -3521,13 +3702,13 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C136">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="E136">
         <v>0.466</v>
@@ -3541,13 +3722,13 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C137">
         <v>4</v>
       </c>
       <c r="D137" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="E137">
         <v>0.4992</v>
@@ -3561,13 +3742,13 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C138">
         <v>5</v>
       </c>
       <c r="D138" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="E138">
         <v>0.3147</v>
@@ -3581,13 +3762,13 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C139">
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E139">
         <v>0.2325</v>
@@ -3601,13 +3782,13 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C140">
         <v>7</v>
       </c>
       <c r="D140" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="E140">
         <v>0.3077</v>
@@ -3621,13 +3802,13 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C141">
         <v>8</v>
       </c>
       <c r="D141" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="E141">
         <v>0.3327</v>
@@ -3641,13 +3822,13 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C142">
         <v>9</v>
       </c>
       <c r="D142" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="E142">
         <v>0.5164</v>
@@ -3661,13 +3842,13 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C143">
         <v>10</v>
       </c>
       <c r="D143" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="E143">
         <v>0.4241</v>
@@ -3681,13 +3862,13 @@
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="E144">
         <v>0.5915</v>
@@ -3701,13 +3882,13 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="E145">
         <v>0.594</v>
@@ -3721,13 +3902,13 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C146">
         <v>3</v>
       </c>
       <c r="D146" t="s">
-        <v>137</v>
+        <v>161</v>
       </c>
       <c r="E146">
         <v>0.6373</v>
@@ -3741,13 +3922,13 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C147">
         <v>4</v>
       </c>
       <c r="D147" t="s">
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="E147">
         <v>0.7056</v>
@@ -3761,13 +3942,13 @@
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C148">
         <v>5</v>
       </c>
       <c r="D148" t="s">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="E148">
         <v>0.6233</v>
@@ -3781,13 +3962,13 @@
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C149">
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="E149">
         <v>0.5113</v>
@@ -3801,13 +3982,13 @@
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C150">
         <v>7</v>
       </c>
       <c r="D150" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="E150">
         <v>0.3871</v>
@@ -3821,13 +4002,13 @@
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C151">
         <v>8</v>
       </c>
       <c r="D151" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="E151">
         <v>0.375</v>
@@ -3841,13 +4022,13 @@
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C152">
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="E152">
         <v>0.4379</v>
@@ -3861,13 +4042,13 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C153">
         <v>10</v>
       </c>
       <c r="D153" t="s">
-        <v>144</v>
+        <v>168</v>
       </c>
       <c r="E153">
         <v>0.5532</v>
@@ -3881,13 +4062,13 @@
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C154">
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="E154">
         <v>0.3674</v>
@@ -3901,13 +4082,13 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E155">
         <v>0.5351</v>
@@ -3921,13 +4102,13 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C156">
         <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E156">
         <v>0.5658</v>
@@ -3941,13 +4122,13 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C157">
         <v>3</v>
       </c>
       <c r="D157" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E157">
         <v>0.8372000000000001</v>
@@ -3961,13 +4142,13 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C158">
         <v>4</v>
       </c>
       <c r="D158" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E158">
         <v>0.6856</v>
@@ -3981,13 +4162,13 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C159">
         <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E159">
         <v>0.4722</v>
@@ -4001,13 +4182,13 @@
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E160">
         <v>0.5958</v>
@@ -4021,13 +4202,13 @@
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C161">
         <v>2</v>
       </c>
       <c r="D161" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E161">
         <v>0.5648</v>
@@ -4041,13 +4222,13 @@
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C162">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E162">
         <v>0.8122</v>
@@ -4061,13 +4242,13 @@
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C163">
         <v>4</v>
       </c>
       <c r="D163" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E163">
         <v>0.5341</v>
@@ -4081,13 +4262,13 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C164">
         <v>5</v>
       </c>
       <c r="D164" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E164">
         <v>0.4946</v>
@@ -4101,13 +4282,13 @@
         <v>18</v>
       </c>
       <c r="B165" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E165">
         <v>0.45</v>
@@ -4121,13 +4302,13 @@
         <v>18</v>
       </c>
       <c r="B166" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C166">
         <v>2</v>
       </c>
       <c r="D166" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E166">
         <v>0.4242</v>
@@ -4141,13 +4322,13 @@
         <v>18</v>
       </c>
       <c r="B167" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C167">
         <v>3</v>
       </c>
       <c r="D167" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E167">
         <v>0.6752</v>
@@ -4161,13 +4342,13 @@
         <v>18</v>
       </c>
       <c r="B168" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C168">
         <v>4</v>
       </c>
       <c r="D168" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E168">
         <v>0.4821</v>
@@ -4181,13 +4362,13 @@
         <v>18</v>
       </c>
       <c r="B169" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C169">
         <v>5</v>
       </c>
       <c r="D169" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E169">
         <v>0.4399</v>
@@ -4201,13 +4382,13 @@
         <v>19</v>
       </c>
       <c r="B170" t="s">
-        <v>35</v>
-      </c>
-      <c r="C170" t="s">
         <v>38</v>
       </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
       <c r="D170" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="E170">
         <v>0.5006</v>
@@ -4221,13 +4402,13 @@
         <v>19</v>
       </c>
       <c r="B171" t="s">
-        <v>35</v>
-      </c>
-      <c r="C171" t="s">
-        <v>39</v>
+        <v>38</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="E171">
         <v>0.5268</v>
@@ -4241,13 +4422,13 @@
         <v>19</v>
       </c>
       <c r="B172" t="s">
-        <v>35</v>
-      </c>
-      <c r="C172" t="s">
-        <v>40</v>
+        <v>38</v>
+      </c>
+      <c r="C172">
+        <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="E172">
         <v>0.8122</v>
@@ -4261,13 +4442,13 @@
         <v>19</v>
       </c>
       <c r="B173" t="s">
-        <v>35</v>
-      </c>
-      <c r="C173" t="s">
-        <v>41</v>
+        <v>38</v>
+      </c>
+      <c r="C173">
+        <v>4</v>
       </c>
       <c r="D173" t="s">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="E173">
         <v>0.5647</v>
@@ -4281,19 +4462,1219 @@
         <v>19</v>
       </c>
       <c r="B174" t="s">
-        <v>35</v>
-      </c>
-      <c r="C174" t="s">
-        <v>42</v>
+        <v>38</v>
+      </c>
+      <c r="C174">
+        <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="E174">
         <v>0.4946</v>
       </c>
       <c r="F174" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
+      <c r="A175" t="s">
+        <v>20</v>
+      </c>
+      <c r="B175" t="s">
+        <v>38</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175" t="s">
+        <v>149</v>
+      </c>
+      <c r="E175">
+        <v>0.4608</v>
+      </c>
+      <c r="F175" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="A176" t="s">
+        <v>20</v>
+      </c>
+      <c r="B176" t="s">
+        <v>38</v>
+      </c>
+      <c r="C176">
+        <v>2</v>
+      </c>
+      <c r="D176" t="s">
+        <v>150</v>
+      </c>
+      <c r="E176">
+        <v>0.6103</v>
+      </c>
+      <c r="F176" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
+      <c r="A177" t="s">
+        <v>20</v>
+      </c>
+      <c r="B177" t="s">
+        <v>38</v>
+      </c>
+      <c r="C177">
+        <v>3</v>
+      </c>
+      <c r="D177" t="s">
+        <v>151</v>
+      </c>
+      <c r="E177">
+        <v>0.6756</v>
+      </c>
+      <c r="F177" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
+      <c r="A178" t="s">
+        <v>20</v>
+      </c>
+      <c r="B178" t="s">
+        <v>38</v>
+      </c>
+      <c r="C178">
+        <v>4</v>
+      </c>
+      <c r="D178" t="s">
+        <v>152</v>
+      </c>
+      <c r="E178">
+        <v>0.5163</v>
+      </c>
+      <c r="F178" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
+      <c r="A179" t="s">
+        <v>20</v>
+      </c>
+      <c r="B179" t="s">
+        <v>38</v>
+      </c>
+      <c r="C179">
+        <v>5</v>
+      </c>
+      <c r="D179" t="s">
+        <v>153</v>
+      </c>
+      <c r="E179">
+        <v>0.4055</v>
+      </c>
+      <c r="F179" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
+      <c r="A180" t="s">
+        <v>21</v>
+      </c>
+      <c r="B180" t="s">
+        <v>41</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180" t="s">
+        <v>170</v>
+      </c>
+      <c r="E180">
+        <v>0.0973</v>
+      </c>
+      <c r="F180" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
+      <c r="A181" t="s">
+        <v>21</v>
+      </c>
+      <c r="B181" t="s">
+        <v>41</v>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+      <c r="D181" t="s">
+        <v>171</v>
+      </c>
+      <c r="E181">
+        <v>0.1698</v>
+      </c>
+      <c r="F181" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
+      <c r="A182" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" t="s">
+        <v>41</v>
+      </c>
+      <c r="C182">
+        <v>3</v>
+      </c>
+      <c r="D182" t="s">
+        <v>172</v>
+      </c>
+      <c r="E182">
+        <v>0.1855</v>
+      </c>
+      <c r="F182" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
+      <c r="A183" t="s">
+        <v>21</v>
+      </c>
+      <c r="B183" t="s">
+        <v>41</v>
+      </c>
+      <c r="C183">
+        <v>4</v>
+      </c>
+      <c r="D183" t="s">
+        <v>173</v>
+      </c>
+      <c r="E183">
+        <v>0.2859</v>
+      </c>
+      <c r="F183" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
+      <c r="A184" t="s">
+        <v>21</v>
+      </c>
+      <c r="B184" t="s">
+        <v>41</v>
+      </c>
+      <c r="C184">
+        <v>5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>174</v>
+      </c>
+      <c r="E184">
+        <v>0.3047</v>
+      </c>
+      <c r="F184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
+      <c r="A185" t="s">
+        <v>21</v>
+      </c>
+      <c r="B185" t="s">
+        <v>41</v>
+      </c>
+      <c r="C185">
+        <v>6</v>
+      </c>
+      <c r="D185" t="s">
+        <v>175</v>
+      </c>
+      <c r="E185">
+        <v>0.1898</v>
+      </c>
+      <c r="F185" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
+      <c r="A186" t="s">
+        <v>21</v>
+      </c>
+      <c r="B186" t="s">
+        <v>41</v>
+      </c>
+      <c r="C186">
+        <v>7</v>
+      </c>
+      <c r="D186" t="s">
+        <v>176</v>
+      </c>
+      <c r="E186">
+        <v>0.1813</v>
+      </c>
+      <c r="F186" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
+      <c r="A187" t="s">
+        <v>21</v>
+      </c>
+      <c r="B187" t="s">
+        <v>41</v>
+      </c>
+      <c r="C187">
+        <v>8</v>
+      </c>
+      <c r="D187" t="s">
+        <v>177</v>
+      </c>
+      <c r="E187">
+        <v>0.082</v>
+      </c>
+      <c r="F187" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
+      <c r="A188" t="s">
+        <v>21</v>
+      </c>
+      <c r="B188" t="s">
+        <v>41</v>
+      </c>
+      <c r="C188">
+        <v>9</v>
+      </c>
+      <c r="D188" t="s">
+        <v>178</v>
+      </c>
+      <c r="E188">
+        <v>0.2175</v>
+      </c>
+      <c r="F188" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189" t="s">
+        <v>41</v>
+      </c>
+      <c r="C189">
+        <v>10</v>
+      </c>
+      <c r="D189" t="s">
+        <v>179</v>
+      </c>
+      <c r="E189">
+        <v>0.2137</v>
+      </c>
+      <c r="F189" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
+      <c r="A190" t="s">
+        <v>21</v>
+      </c>
+      <c r="B190" t="s">
+        <v>41</v>
+      </c>
+      <c r="C190">
+        <v>11</v>
+      </c>
+      <c r="D190" t="s">
+        <v>180</v>
+      </c>
+      <c r="E190">
+        <v>0.2007</v>
+      </c>
+      <c r="F190" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
+      <c r="A191" t="s">
+        <v>21</v>
+      </c>
+      <c r="B191" t="s">
+        <v>41</v>
+      </c>
+      <c r="C191">
+        <v>12</v>
+      </c>
+      <c r="D191" t="s">
+        <v>181</v>
+      </c>
+      <c r="E191">
+        <v>0.1036</v>
+      </c>
+      <c r="F191" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
+      <c r="A192" t="s">
+        <v>21</v>
+      </c>
+      <c r="B192" t="s">
+        <v>41</v>
+      </c>
+      <c r="C192">
+        <v>13</v>
+      </c>
+      <c r="D192" t="s">
+        <v>182</v>
+      </c>
+      <c r="E192">
+        <v>0.2143</v>
+      </c>
+      <c r="F192" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
+      <c r="A193" t="s">
+        <v>21</v>
+      </c>
+      <c r="B193" t="s">
+        <v>41</v>
+      </c>
+      <c r="C193">
+        <v>14</v>
+      </c>
+      <c r="D193" t="s">
+        <v>183</v>
+      </c>
+      <c r="E193">
+        <v>0.1146</v>
+      </c>
+      <c r="F193" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
+      <c r="A194" t="s">
+        <v>21</v>
+      </c>
+      <c r="B194" t="s">
+        <v>41</v>
+      </c>
+      <c r="C194">
+        <v>15</v>
+      </c>
+      <c r="D194" t="s">
+        <v>184</v>
+      </c>
+      <c r="E194">
+        <v>0.1555</v>
+      </c>
+      <c r="F194" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
+      <c r="A195" t="s">
+        <v>21</v>
+      </c>
+      <c r="B195" t="s">
+        <v>41</v>
+      </c>
+      <c r="C195">
+        <v>16</v>
+      </c>
+      <c r="D195" t="s">
+        <v>185</v>
+      </c>
+      <c r="E195">
+        <v>0.3266</v>
+      </c>
+      <c r="F195" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
+      <c r="A196" t="s">
+        <v>21</v>
+      </c>
+      <c r="B196" t="s">
+        <v>41</v>
+      </c>
+      <c r="C196">
+        <v>17</v>
+      </c>
+      <c r="D196" t="s">
+        <v>186</v>
+      </c>
+      <c r="E196">
+        <v>0.2117</v>
+      </c>
+      <c r="F196" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
+      <c r="A197" t="s">
+        <v>21</v>
+      </c>
+      <c r="B197" t="s">
+        <v>41</v>
+      </c>
+      <c r="C197">
+        <v>18</v>
+      </c>
+      <c r="D197" t="s">
+        <v>187</v>
+      </c>
+      <c r="E197">
+        <v>0.3606</v>
+      </c>
+      <c r="F197" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
+      <c r="A198" t="s">
+        <v>21</v>
+      </c>
+      <c r="B198" t="s">
+        <v>41</v>
+      </c>
+      <c r="C198">
+        <v>19</v>
+      </c>
+      <c r="D198" t="s">
+        <v>188</v>
+      </c>
+      <c r="E198">
+        <v>0.2731</v>
+      </c>
+      <c r="F198" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
+      <c r="A199" t="s">
+        <v>21</v>
+      </c>
+      <c r="B199" t="s">
+        <v>41</v>
+      </c>
+      <c r="C199">
+        <v>20</v>
+      </c>
+      <c r="D199" t="s">
+        <v>189</v>
+      </c>
+      <c r="E199">
+        <v>0.298</v>
+      </c>
+      <c r="F199" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
+      <c r="A200" t="s">
+        <v>21</v>
+      </c>
+      <c r="B200" t="s">
+        <v>41</v>
+      </c>
+      <c r="C200">
+        <v>21</v>
+      </c>
+      <c r="D200" t="s">
+        <v>190</v>
+      </c>
+      <c r="E200">
+        <v>0.2657</v>
+      </c>
+      <c r="F200" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
+      <c r="A201" t="s">
+        <v>21</v>
+      </c>
+      <c r="B201" t="s">
+        <v>41</v>
+      </c>
+      <c r="C201">
+        <v>22</v>
+      </c>
+      <c r="D201" t="s">
+        <v>191</v>
+      </c>
+      <c r="E201">
+        <v>0.2808</v>
+      </c>
+      <c r="F201" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
+      <c r="A202" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202" t="s">
+        <v>41</v>
+      </c>
+      <c r="C202">
+        <v>23</v>
+      </c>
+      <c r="D202" t="s">
+        <v>192</v>
+      </c>
+      <c r="E202">
+        <v>0.2233</v>
+      </c>
+      <c r="F202" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
+      <c r="A203" t="s">
+        <v>21</v>
+      </c>
+      <c r="B203" t="s">
+        <v>41</v>
+      </c>
+      <c r="C203">
+        <v>24</v>
+      </c>
+      <c r="D203" t="s">
+        <v>193</v>
+      </c>
+      <c r="E203">
+        <v>0.1682</v>
+      </c>
+      <c r="F203" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
+      <c r="A204" t="s">
+        <v>22</v>
+      </c>
+      <c r="B204" t="s">
+        <v>42</v>
+      </c>
+      <c r="C204">
+        <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>194</v>
+      </c>
+      <c r="E204">
+        <v>0.18</v>
+      </c>
+      <c r="F204" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
+      <c r="A205" t="s">
+        <v>22</v>
+      </c>
+      <c r="B205" t="s">
+        <v>42</v>
+      </c>
+      <c r="C205">
+        <v>2</v>
+      </c>
+      <c r="D205" t="s">
+        <v>195</v>
+      </c>
+      <c r="E205">
+        <v>0.1933</v>
+      </c>
+      <c r="F205" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
+      <c r="A206" t="s">
+        <v>22</v>
+      </c>
+      <c r="B206" t="s">
+        <v>42</v>
+      </c>
+      <c r="C206">
+        <v>3</v>
+      </c>
+      <c r="D206" t="s">
+        <v>196</v>
+      </c>
+      <c r="E206">
+        <v>0.1658</v>
+      </c>
+      <c r="F206" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
+      <c r="A207" t="s">
+        <v>22</v>
+      </c>
+      <c r="B207" t="s">
+        <v>42</v>
+      </c>
+      <c r="C207">
+        <v>4</v>
+      </c>
+      <c r="D207" t="s">
+        <v>197</v>
+      </c>
+      <c r="E207">
+        <v>0.2125</v>
+      </c>
+      <c r="F207" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
+      <c r="A208" t="s">
+        <v>22</v>
+      </c>
+      <c r="B208" t="s">
+        <v>42</v>
+      </c>
+      <c r="C208">
+        <v>5</v>
+      </c>
+      <c r="D208" t="s">
+        <v>198</v>
+      </c>
+      <c r="E208">
+        <v>0.3514</v>
+      </c>
+      <c r="F208" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
+      <c r="A209" t="s">
+        <v>22</v>
+      </c>
+      <c r="B209" t="s">
+        <v>42</v>
+      </c>
+      <c r="C209">
+        <v>6</v>
+      </c>
+      <c r="D209" t="s">
+        <v>199</v>
+      </c>
+      <c r="E209">
+        <v>0.2825</v>
+      </c>
+      <c r="F209" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
+      <c r="A210" t="s">
+        <v>22</v>
+      </c>
+      <c r="B210" t="s">
+        <v>42</v>
+      </c>
+      <c r="C210">
+        <v>7</v>
+      </c>
+      <c r="D210" t="s">
+        <v>200</v>
+      </c>
+      <c r="E210">
+        <v>0.2293</v>
+      </c>
+      <c r="F210" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
+      <c r="A211" t="s">
+        <v>22</v>
+      </c>
+      <c r="B211" t="s">
+        <v>41</v>
+      </c>
+      <c r="C211" t="s">
+        <v>43</v>
+      </c>
+      <c r="D211" t="s">
+        <v>170</v>
+      </c>
+      <c r="E211">
+        <v>0.1449</v>
+      </c>
+      <c r="F211" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
+      <c r="A212" t="s">
+        <v>22</v>
+      </c>
+      <c r="B212" t="s">
+        <v>41</v>
+      </c>
+      <c r="C212" t="s">
+        <v>44</v>
+      </c>
+      <c r="D212" t="s">
+        <v>171</v>
+      </c>
+      <c r="E212">
+        <v>0.1865</v>
+      </c>
+      <c r="F212" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
+      <c r="A213" t="s">
+        <v>22</v>
+      </c>
+      <c r="B213" t="s">
+        <v>41</v>
+      </c>
+      <c r="C213" t="s">
+        <v>45</v>
+      </c>
+      <c r="D213" t="s">
+        <v>172</v>
+      </c>
+      <c r="E213">
+        <v>0.2748</v>
+      </c>
+      <c r="F213" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
+      <c r="A214" t="s">
+        <v>22</v>
+      </c>
+      <c r="B214" t="s">
+        <v>41</v>
+      </c>
+      <c r="C214" t="s">
+        <v>46</v>
+      </c>
+      <c r="D214" t="s">
+        <v>173</v>
+      </c>
+      <c r="E214">
+        <v>0.3114</v>
+      </c>
+      <c r="F214" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
+      <c r="A215" t="s">
+        <v>22</v>
+      </c>
+      <c r="B215" t="s">
+        <v>41</v>
+      </c>
+      <c r="C215" t="s">
+        <v>47</v>
+      </c>
+      <c r="D215" t="s">
+        <v>174</v>
+      </c>
+      <c r="E215">
+        <v>0.3704</v>
+      </c>
+      <c r="F215" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
+      <c r="A216" t="s">
+        <v>22</v>
+      </c>
+      <c r="B216" t="s">
+        <v>41</v>
+      </c>
+      <c r="C216" t="s">
+        <v>48</v>
+      </c>
+      <c r="D216" t="s">
+        <v>175</v>
+      </c>
+      <c r="E216">
+        <v>0.2685</v>
+      </c>
+      <c r="F216" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
+      <c r="A217" t="s">
+        <v>22</v>
+      </c>
+      <c r="B217" t="s">
+        <v>41</v>
+      </c>
+      <c r="C217" t="s">
+        <v>49</v>
+      </c>
+      <c r="D217" t="s">
+        <v>176</v>
+      </c>
+      <c r="E217">
+        <v>0.1876</v>
+      </c>
+      <c r="F217" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
+      <c r="A218" t="s">
+        <v>22</v>
+      </c>
+      <c r="B218" t="s">
+        <v>41</v>
+      </c>
+      <c r="C218" t="s">
+        <v>50</v>
+      </c>
+      <c r="D218" t="s">
+        <v>177</v>
+      </c>
+      <c r="E218">
+        <v>0.1371</v>
+      </c>
+      <c r="F218" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
+      <c r="A219" t="s">
+        <v>22</v>
+      </c>
+      <c r="B219" t="s">
+        <v>41</v>
+      </c>
+      <c r="C219" t="s">
+        <v>51</v>
+      </c>
+      <c r="D219" t="s">
+        <v>178</v>
+      </c>
+      <c r="E219">
+        <v>0.2504</v>
+      </c>
+      <c r="F219" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
+      <c r="A220" t="s">
+        <v>22</v>
+      </c>
+      <c r="B220" t="s">
+        <v>41</v>
+      </c>
+      <c r="C220" t="s">
+        <v>52</v>
+      </c>
+      <c r="D220" t="s">
+        <v>179</v>
+      </c>
+      <c r="E220">
+        <v>0.2874</v>
+      </c>
+      <c r="F220" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
+      <c r="A221" t="s">
+        <v>22</v>
+      </c>
+      <c r="B221" t="s">
+        <v>41</v>
+      </c>
+      <c r="C221" t="s">
+        <v>53</v>
+      </c>
+      <c r="D221" t="s">
+        <v>180</v>
+      </c>
+      <c r="E221">
+        <v>0.2726</v>
+      </c>
+      <c r="F221" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
+      <c r="A222" t="s">
+        <v>22</v>
+      </c>
+      <c r="B222" t="s">
+        <v>41</v>
+      </c>
+      <c r="C222" t="s">
+        <v>54</v>
+      </c>
+      <c r="D222" t="s">
+        <v>181</v>
+      </c>
+      <c r="E222">
+        <v>0.1568</v>
+      </c>
+      <c r="F222" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
+      <c r="A223" t="s">
+        <v>22</v>
+      </c>
+      <c r="B223" t="s">
+        <v>41</v>
+      </c>
+      <c r="C223" t="s">
+        <v>55</v>
+      </c>
+      <c r="D223" t="s">
+        <v>182</v>
+      </c>
+      <c r="E223">
+        <v>0.2373</v>
+      </c>
+      <c r="F223" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
+      <c r="A224" t="s">
+        <v>22</v>
+      </c>
+      <c r="B224" t="s">
+        <v>41</v>
+      </c>
+      <c r="C224" t="s">
+        <v>56</v>
+      </c>
+      <c r="D224" t="s">
+        <v>183</v>
+      </c>
+      <c r="E224">
+        <v>0.2109</v>
+      </c>
+      <c r="F224" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
+      <c r="A225" t="s">
+        <v>22</v>
+      </c>
+      <c r="B225" t="s">
+        <v>41</v>
+      </c>
+      <c r="C225" t="s">
+        <v>57</v>
+      </c>
+      <c r="D225" t="s">
+        <v>184</v>
+      </c>
+      <c r="E225">
+        <v>0.2147</v>
+      </c>
+      <c r="F225" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
+      <c r="A226" t="s">
+        <v>22</v>
+      </c>
+      <c r="B226" t="s">
+        <v>41</v>
+      </c>
+      <c r="C226" t="s">
+        <v>58</v>
+      </c>
+      <c r="D226" t="s">
+        <v>185</v>
+      </c>
+      <c r="E226">
+        <v>0.3517</v>
+      </c>
+      <c r="F226" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
+      <c r="A227" t="s">
+        <v>22</v>
+      </c>
+      <c r="B227" t="s">
+        <v>41</v>
+      </c>
+      <c r="C227" t="s">
+        <v>59</v>
+      </c>
+      <c r="D227" t="s">
+        <v>186</v>
+      </c>
+      <c r="E227">
+        <v>0.2691</v>
+      </c>
+      <c r="F227" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
+      <c r="A228" t="s">
+        <v>22</v>
+      </c>
+      <c r="B228" t="s">
+        <v>41</v>
+      </c>
+      <c r="C228" t="s">
+        <v>60</v>
+      </c>
+      <c r="D228" t="s">
+        <v>187</v>
+      </c>
+      <c r="E228">
+        <v>0.4198</v>
+      </c>
+      <c r="F228" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
+      <c r="A229" t="s">
+        <v>22</v>
+      </c>
+      <c r="B229" t="s">
+        <v>41</v>
+      </c>
+      <c r="C229" t="s">
+        <v>61</v>
+      </c>
+      <c r="D229" t="s">
+        <v>188</v>
+      </c>
+      <c r="E229">
+        <v>0.3182</v>
+      </c>
+      <c r="F229" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
+      <c r="A230" t="s">
+        <v>22</v>
+      </c>
+      <c r="B230" t="s">
+        <v>41</v>
+      </c>
+      <c r="C230" t="s">
+        <v>62</v>
+      </c>
+      <c r="D230" t="s">
+        <v>189</v>
+      </c>
+      <c r="E230">
+        <v>0.4125</v>
+      </c>
+      <c r="F230" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
+      <c r="A231" t="s">
+        <v>22</v>
+      </c>
+      <c r="B231" t="s">
+        <v>41</v>
+      </c>
+      <c r="C231" t="s">
+        <v>63</v>
+      </c>
+      <c r="D231" t="s">
+        <v>190</v>
+      </c>
+      <c r="E231">
+        <v>0.3677</v>
+      </c>
+      <c r="F231" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
+      <c r="A232" t="s">
+        <v>22</v>
+      </c>
+      <c r="B232" t="s">
+        <v>41</v>
+      </c>
+      <c r="C232" t="s">
+        <v>64</v>
+      </c>
+      <c r="D232" t="s">
+        <v>191</v>
+      </c>
+      <c r="E232">
+        <v>0.3396</v>
+      </c>
+      <c r="F232" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
+      <c r="A233" t="s">
+        <v>22</v>
+      </c>
+      <c r="B233" t="s">
+        <v>41</v>
+      </c>
+      <c r="C233" t="s">
+        <v>65</v>
+      </c>
+      <c r="D233" t="s">
+        <v>192</v>
+      </c>
+      <c r="E233">
+        <v>0.2825</v>
+      </c>
+      <c r="F233" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
+      <c r="A234" t="s">
+        <v>22</v>
+      </c>
+      <c r="B234" t="s">
+        <v>41</v>
+      </c>
+      <c r="C234" t="s">
+        <v>66</v>
+      </c>
+      <c r="D234" t="s">
+        <v>193</v>
+      </c>
+      <c r="E234">
+        <v>0.2293</v>
+      </c>
+      <c r="F234" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/backend/POC/prefilter_cache.xlsx
+++ b/backend/POC/prefilter_cache.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="189">
   <si>
     <t>process_hash</t>
   </si>
@@ -85,6 +85,21 @@
     <t>b4d05022165f08ab</t>
   </si>
   <si>
+    <t>c3d8f99ddd88e162</t>
+  </si>
+  <si>
+    <t>1cac12b2c09db3c7</t>
+  </si>
+  <si>
+    <t>771aa2b895dfa748</t>
+  </si>
+  <si>
+    <t>2bd4f6ce8e05cf75</t>
+  </si>
+  <si>
+    <t>81e3a116d20744c2</t>
+  </si>
+  <si>
     <t>synthetic-compliance-rules-#1</t>
   </si>
   <si>
@@ -164,57 +179,6 @@
   </si>
   <si>
     <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>24</t>
   </si>
   <si>
     <t>All payment service providers shall conduct a comprehensive identity verification of each merchant prior to granting access to payment processing services.</t>
@@ -994,7 +958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F234"/>
+  <dimension ref="A1:F292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1022,13 +986,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C2">
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E2">
         <v>0.5838</v>
@@ -1042,13 +1006,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E3">
         <v>0.6263</v>
@@ -1062,13 +1026,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C4">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E4">
         <v>0.6303</v>
@@ -1082,13 +1046,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>0.6439</v>
@@ -1102,13 +1066,13 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="E6">
         <v>0.4402</v>
@@ -1122,13 +1086,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="E7">
         <v>0.6491</v>
@@ -1142,13 +1106,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E8">
         <v>0.6712</v>
@@ -1162,13 +1126,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E9">
         <v>0.5116000000000001</v>
@@ -1182,13 +1146,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C10">
         <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E10">
         <v>0.5103</v>
@@ -1202,13 +1166,13 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C11">
         <v>16</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E11">
         <v>0.521</v>
@@ -1222,13 +1186,13 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>17</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E12">
         <v>0.7005</v>
@@ -1242,13 +1206,13 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E13">
         <v>0.4253</v>
@@ -1262,13 +1226,13 @@
         <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>19</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="E14">
         <v>0.4379</v>
@@ -1282,13 +1246,13 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C15">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E15">
         <v>0.6097</v>
@@ -1302,13 +1266,13 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C16">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="E16">
         <v>0.4384</v>
@@ -1322,13 +1286,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C17">
         <v>22</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E17">
         <v>0.427</v>
@@ -1342,13 +1306,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C18">
         <v>27</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E18">
         <v>0.6855</v>
@@ -1362,13 +1326,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C19">
         <v>28</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E19">
         <v>0.5853</v>
@@ -1382,13 +1346,13 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>29</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E20">
         <v>0.7211</v>
@@ -1402,13 +1366,13 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="E21">
         <v>0.5838</v>
@@ -1422,13 +1386,13 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E22">
         <v>0.6777</v>
@@ -1442,13 +1406,13 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="E23">
         <v>0.6778999999999999</v>
@@ -1462,13 +1426,13 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E24">
         <v>0.6841</v>
@@ -1482,13 +1446,13 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C25">
         <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E25">
         <v>0.6841</v>
@@ -1502,13 +1466,13 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E26">
         <v>0.6841</v>
@@ -1522,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="E27">
         <v>0.6841</v>
@@ -1542,13 +1506,13 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E28">
         <v>0.5894</v>
@@ -1562,13 +1526,13 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C29">
         <v>2</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E29">
         <v>0.6067</v>
@@ -1582,13 +1546,13 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E30">
         <v>0.6036</v>
@@ -1602,13 +1566,13 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E31">
         <v>0.6428</v>
@@ -1622,13 +1586,13 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E32">
         <v>0.4052</v>
@@ -1642,13 +1606,13 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C33">
         <v>6</v>
       </c>
       <c r="D33" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E33">
         <v>0.625</v>
@@ -1662,13 +1626,13 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C34">
         <v>7</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E34">
         <v>0.6039</v>
@@ -1682,13 +1646,13 @@
         <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="E35">
         <v>0.6194</v>
@@ -1702,13 +1666,13 @@
         <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>2</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E36">
         <v>0.6367</v>
@@ -1722,13 +1686,13 @@
         <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="E37">
         <v>0.6216</v>
@@ -1742,13 +1706,13 @@
         <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E38">
         <v>0.6395999999999999</v>
@@ -1762,13 +1726,13 @@
         <v>6</v>
       </c>
       <c r="B39" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="E39">
         <v>0.6151</v>
@@ -1782,13 +1746,13 @@
         <v>6</v>
       </c>
       <c r="B40" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C40">
         <v>2</v>
       </c>
       <c r="D40" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="E40">
         <v>0.6411</v>
@@ -1802,13 +1766,13 @@
         <v>6</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="E41">
         <v>0.4462</v>
@@ -1822,13 +1786,13 @@
         <v>6</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>4</v>
       </c>
       <c r="D42" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E42">
         <v>0.5122</v>
@@ -1842,13 +1806,13 @@
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>1</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="E43">
         <v>0.5894</v>
@@ -1862,13 +1826,13 @@
         <v>6</v>
       </c>
       <c r="B44" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>2</v>
       </c>
       <c r="D44" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="E44">
         <v>0.6067</v>
@@ -1882,13 +1846,13 @@
         <v>6</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E45">
         <v>0.6036</v>
@@ -1902,13 +1866,13 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C46">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="E46">
         <v>0.6428</v>
@@ -1922,13 +1886,13 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C47">
         <v>5</v>
       </c>
       <c r="D47" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E47">
         <v>0.4052</v>
@@ -1942,13 +1906,13 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C48">
         <v>6</v>
       </c>
       <c r="D48" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E48">
         <v>0.625</v>
@@ -1962,13 +1926,13 @@
         <v>6</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C49">
         <v>7</v>
       </c>
       <c r="D49" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="E49">
         <v>0.6039</v>
@@ -1982,13 +1946,13 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C50">
         <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="E50">
         <v>0.4927</v>
@@ -2002,13 +1966,13 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E51">
         <v>0.6346000000000001</v>
@@ -2022,13 +1986,13 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C52">
         <v>2</v>
       </c>
       <c r="D52" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E52">
         <v>0.3461</v>
@@ -2042,13 +2006,13 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E53">
         <v>0.15</v>
@@ -2062,13 +2026,13 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C54">
         <v>4</v>
       </c>
       <c r="D54" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E54">
         <v>0.4212</v>
@@ -2082,13 +2046,13 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C55">
         <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E55">
         <v>0.3107</v>
@@ -2102,13 +2066,13 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C56">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E56">
         <v>0.2965</v>
@@ -2122,13 +2086,13 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C57">
         <v>7</v>
       </c>
       <c r="D57" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E57">
         <v>0.2812</v>
@@ -2142,13 +2106,13 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C58">
         <v>8</v>
       </c>
       <c r="D58" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E58">
         <v>0.2349</v>
@@ -2162,13 +2126,13 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C59">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="E59">
         <v>0.6031</v>
@@ -2182,13 +2146,13 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C60">
         <v>10</v>
       </c>
       <c r="D60" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="E60">
         <v>0.4668</v>
@@ -2202,13 +2166,13 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C61">
         <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E61">
         <v>0.4043</v>
@@ -2222,13 +2186,13 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C62">
         <v>2</v>
       </c>
       <c r="D62" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E62">
         <v>0.496</v>
@@ -2242,13 +2206,13 @@
         <v>8</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E63">
         <v>0.4781</v>
@@ -2262,13 +2226,13 @@
         <v>8</v>
       </c>
       <c r="B64" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C64">
         <v>4</v>
       </c>
       <c r="D64" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E64">
         <v>0.5125</v>
@@ -2282,13 +2246,13 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C65">
         <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E65">
         <v>0.3548</v>
@@ -2302,13 +2266,13 @@
         <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C66">
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E66">
         <v>0.2212</v>
@@ -2322,13 +2286,13 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C67">
         <v>7</v>
       </c>
       <c r="D67" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E67">
         <v>0.3205</v>
@@ -2342,13 +2306,13 @@
         <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C68">
         <v>8</v>
       </c>
       <c r="D68" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E68">
         <v>0.2504</v>
@@ -2362,13 +2326,13 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E69">
         <v>0.51</v>
@@ -2382,13 +2346,13 @@
         <v>8</v>
       </c>
       <c r="B70" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C70">
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E70">
         <v>0.4057</v>
@@ -2402,13 +2366,13 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E71">
         <v>0.6163999999999999</v>
@@ -2422,13 +2386,13 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C72">
         <v>2</v>
       </c>
       <c r="D72" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E72">
         <v>0.5685</v>
@@ -2442,13 +2406,13 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E73">
         <v>0.6151</v>
@@ -2462,13 +2426,13 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C74">
         <v>4</v>
       </c>
       <c r="D74" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E74">
         <v>0.6232</v>
@@ -2482,13 +2446,13 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C75">
         <v>5</v>
       </c>
       <c r="D75" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E75">
         <v>0.5322</v>
@@ -2502,13 +2466,13 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C76">
         <v>6</v>
       </c>
       <c r="D76" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E76">
         <v>0.3512</v>
@@ -2522,13 +2486,13 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C77">
         <v>7</v>
       </c>
       <c r="D77" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E77">
         <v>0.4761</v>
@@ -2542,13 +2506,13 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C78">
         <v>8</v>
       </c>
       <c r="D78" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E78">
         <v>0.481</v>
@@ -2562,13 +2526,13 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C79">
         <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E79">
         <v>0.5723</v>
@@ -2582,13 +2546,13 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C80">
         <v>10</v>
       </c>
       <c r="D80" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E80">
         <v>0.6477000000000001</v>
@@ -2602,13 +2566,13 @@
         <v>10</v>
       </c>
       <c r="B81" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C81">
         <v>1</v>
       </c>
       <c r="D81" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E81">
         <v>0.4285</v>
@@ -2622,13 +2586,13 @@
         <v>10</v>
       </c>
       <c r="B82" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E82">
         <v>0.5831</v>
@@ -2642,13 +2606,13 @@
         <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E83">
         <v>0.3756</v>
@@ -2662,13 +2626,13 @@
         <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C84">
         <v>4</v>
       </c>
       <c r="D84" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E84">
         <v>0.4707</v>
@@ -2682,13 +2646,13 @@
         <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C85">
         <v>5</v>
       </c>
       <c r="D85" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E85">
         <v>0.4945</v>
@@ -2702,13 +2666,13 @@
         <v>10</v>
       </c>
       <c r="B86" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C86">
         <v>6</v>
       </c>
       <c r="D86" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E86">
         <v>0.3551</v>
@@ -2722,13 +2686,13 @@
         <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C87">
         <v>7</v>
       </c>
       <c r="D87" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E87">
         <v>0.5426</v>
@@ -2742,13 +2706,13 @@
         <v>10</v>
       </c>
       <c r="B88" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C88">
         <v>8</v>
       </c>
       <c r="D88" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E88">
         <v>0.5185999999999999</v>
@@ -2762,13 +2726,13 @@
         <v>10</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C89">
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="E89">
         <v>0.3634</v>
@@ -2782,13 +2746,13 @@
         <v>10</v>
       </c>
       <c r="B90" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C90">
         <v>10</v>
       </c>
       <c r="D90" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="E90">
         <v>0.4161</v>
@@ -2802,13 +2766,13 @@
         <v>10</v>
       </c>
       <c r="B91" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C91">
         <v>11</v>
       </c>
       <c r="D91" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="E91">
         <v>0.2871</v>
@@ -2822,13 +2786,13 @@
         <v>10</v>
       </c>
       <c r="B92" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C92">
         <v>12</v>
       </c>
       <c r="D92" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E92">
         <v>0.506</v>
@@ -2842,13 +2806,13 @@
         <v>10</v>
       </c>
       <c r="B93" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C93">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E93">
         <v>0.4668</v>
@@ -2862,13 +2826,13 @@
         <v>10</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C94">
         <v>14</v>
       </c>
       <c r="D94" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E94">
         <v>0.3633</v>
@@ -2882,13 +2846,13 @@
         <v>10</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C95">
         <v>15</v>
       </c>
       <c r="D95" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="E95">
         <v>0.3922</v>
@@ -2902,13 +2866,13 @@
         <v>10</v>
       </c>
       <c r="B96" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C96">
         <v>16</v>
       </c>
       <c r="D96" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E96">
         <v>0.4302</v>
@@ -2922,13 +2886,13 @@
         <v>10</v>
       </c>
       <c r="B97" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C97">
         <v>17</v>
       </c>
       <c r="D97" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="E97">
         <v>0.4779</v>
@@ -2942,13 +2906,13 @@
         <v>10</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C98">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E98">
         <v>0.4652</v>
@@ -2962,13 +2926,13 @@
         <v>10</v>
       </c>
       <c r="B99" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C99">
         <v>19</v>
       </c>
       <c r="D99" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="E99">
         <v>0.4672</v>
@@ -2982,13 +2946,13 @@
         <v>10</v>
       </c>
       <c r="B100" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C100">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E100">
         <v>0.4137</v>
@@ -3002,13 +2966,13 @@
         <v>10</v>
       </c>
       <c r="B101" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C101">
         <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="E101">
         <v>0.3759</v>
@@ -3022,13 +2986,13 @@
         <v>10</v>
       </c>
       <c r="B102" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C102">
         <v>22</v>
       </c>
       <c r="D102" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="E102">
         <v>0.3841</v>
@@ -3042,13 +3006,13 @@
         <v>10</v>
       </c>
       <c r="B103" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C103">
         <v>23</v>
       </c>
       <c r="D103" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E103">
         <v>0.377</v>
@@ -3062,13 +3026,13 @@
         <v>11</v>
       </c>
       <c r="B104" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E104">
         <v>0.589</v>
@@ -3082,13 +3046,13 @@
         <v>11</v>
       </c>
       <c r="B105" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E105">
         <v>0.5769</v>
@@ -3102,13 +3066,13 @@
         <v>11</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E106">
         <v>0.8023</v>
@@ -3122,13 +3086,13 @@
         <v>11</v>
       </c>
       <c r="B107" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C107">
         <v>4</v>
       </c>
       <c r="D107" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E107">
         <v>0.6107</v>
@@ -3142,13 +3106,13 @@
         <v>11</v>
       </c>
       <c r="B108" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C108">
         <v>5</v>
       </c>
       <c r="D108" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E108">
         <v>0.5578</v>
@@ -3162,13 +3126,13 @@
         <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C109">
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="E109">
         <v>0.525</v>
@@ -3182,13 +3146,13 @@
         <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E110">
         <v>0.6331</v>
@@ -3202,13 +3166,13 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E111">
         <v>0.6157</v>
@@ -3222,13 +3186,13 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C112">
         <v>4</v>
       </c>
       <c r="D112" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E112">
         <v>0.5907</v>
@@ -3242,13 +3206,13 @@
         <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C113">
         <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E113">
         <v>0.5887</v>
@@ -3262,13 +3226,13 @@
         <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C114">
         <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E114">
         <v>0.4681</v>
@@ -3282,13 +3246,13 @@
         <v>13</v>
       </c>
       <c r="B115" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E115">
         <v>0.5196</v>
@@ -3302,13 +3266,13 @@
         <v>13</v>
       </c>
       <c r="B116" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E116">
         <v>0.4807</v>
@@ -3322,13 +3286,13 @@
         <v>13</v>
       </c>
       <c r="B117" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C117">
         <v>4</v>
       </c>
       <c r="D117" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E117">
         <v>0.5272</v>
@@ -3342,13 +3306,13 @@
         <v>13</v>
       </c>
       <c r="B118" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C118">
         <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E118">
         <v>0.4035</v>
@@ -3362,13 +3326,13 @@
         <v>13</v>
       </c>
       <c r="B119" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C119">
         <v>6</v>
       </c>
       <c r="D119" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E119">
         <v>0.2197</v>
@@ -3382,13 +3346,13 @@
         <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C120">
         <v>7</v>
       </c>
       <c r="D120" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E120">
         <v>0.3409</v>
@@ -3402,13 +3366,13 @@
         <v>13</v>
       </c>
       <c r="B121" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C121">
         <v>8</v>
       </c>
       <c r="D121" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E121">
         <v>0.306</v>
@@ -3422,13 +3386,13 @@
         <v>13</v>
       </c>
       <c r="B122" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C122">
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E122">
         <v>0.5057</v>
@@ -3442,13 +3406,13 @@
         <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C123">
         <v>10</v>
       </c>
       <c r="D123" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E123">
         <v>0.391</v>
@@ -3462,13 +3426,13 @@
         <v>14</v>
       </c>
       <c r="B124" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C124">
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E124">
         <v>0.4744</v>
@@ -3482,13 +3446,13 @@
         <v>14</v>
       </c>
       <c r="B125" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E125">
         <v>0.5164</v>
@@ -3502,13 +3466,13 @@
         <v>14</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C126">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E126">
         <v>0.4936</v>
@@ -3522,13 +3486,13 @@
         <v>14</v>
       </c>
       <c r="B127" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C127">
         <v>4</v>
       </c>
       <c r="D127" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E127">
         <v>0.5272</v>
@@ -3542,13 +3506,13 @@
         <v>14</v>
       </c>
       <c r="B128" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C128">
         <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E128">
         <v>0.3482</v>
@@ -3562,13 +3526,13 @@
         <v>14</v>
       </c>
       <c r="B129" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C129">
         <v>6</v>
       </c>
       <c r="D129" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E129">
         <v>0.2297</v>
@@ -3582,13 +3546,13 @@
         <v>14</v>
       </c>
       <c r="B130" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C130">
         <v>7</v>
       </c>
       <c r="D130" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E130">
         <v>0.3378</v>
@@ -3602,13 +3566,13 @@
         <v>14</v>
       </c>
       <c r="B131" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C131">
         <v>8</v>
       </c>
       <c r="D131" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E131">
         <v>0.3239</v>
@@ -3622,13 +3586,13 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C132">
         <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E132">
         <v>0.5134</v>
@@ -3642,13 +3606,13 @@
         <v>14</v>
       </c>
       <c r="B133" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C133">
         <v>10</v>
       </c>
       <c r="D133" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E133">
         <v>0.4012</v>
@@ -3662,13 +3626,13 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E134">
         <v>0.4637</v>
@@ -3682,13 +3646,13 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C135">
         <v>2</v>
       </c>
       <c r="D135" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E135">
         <v>0.5274</v>
@@ -3702,13 +3666,13 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C136">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E136">
         <v>0.466</v>
@@ -3722,13 +3686,13 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C137">
         <v>4</v>
       </c>
       <c r="D137" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E137">
         <v>0.4992</v>
@@ -3742,13 +3706,13 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C138">
         <v>5</v>
       </c>
       <c r="D138" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E138">
         <v>0.3147</v>
@@ -3762,13 +3726,13 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C139">
         <v>6</v>
       </c>
       <c r="D139" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E139">
         <v>0.2325</v>
@@ -3782,13 +3746,13 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C140">
         <v>7</v>
       </c>
       <c r="D140" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="E140">
         <v>0.3077</v>
@@ -3802,13 +3766,13 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C141">
         <v>8</v>
       </c>
       <c r="D141" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E141">
         <v>0.3327</v>
@@ -3822,13 +3786,13 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C142">
         <v>9</v>
       </c>
       <c r="D142" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E142">
         <v>0.5164</v>
@@ -3842,13 +3806,13 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C143">
         <v>10</v>
       </c>
       <c r="D143" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E143">
         <v>0.4241</v>
@@ -3862,13 +3826,13 @@
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="D144" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E144">
         <v>0.5915</v>
@@ -3882,13 +3846,13 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C145">
         <v>2</v>
       </c>
       <c r="D145" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E145">
         <v>0.594</v>
@@ -3902,13 +3866,13 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C146">
         <v>3</v>
       </c>
       <c r="D146" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E146">
         <v>0.6373</v>
@@ -3922,13 +3886,13 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C147">
         <v>4</v>
       </c>
       <c r="D147" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="E147">
         <v>0.7056</v>
@@ -3942,13 +3906,13 @@
         <v>6</v>
       </c>
       <c r="B148" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C148">
         <v>5</v>
       </c>
       <c r="D148" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="E148">
         <v>0.6233</v>
@@ -3962,13 +3926,13 @@
         <v>6</v>
       </c>
       <c r="B149" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C149">
         <v>6</v>
       </c>
       <c r="D149" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E149">
         <v>0.5113</v>
@@ -3982,13 +3946,13 @@
         <v>6</v>
       </c>
       <c r="B150" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C150">
         <v>7</v>
       </c>
       <c r="D150" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E150">
         <v>0.3871</v>
@@ -4002,13 +3966,13 @@
         <v>6</v>
       </c>
       <c r="B151" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C151">
         <v>8</v>
       </c>
       <c r="D151" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E151">
         <v>0.375</v>
@@ -4022,13 +3986,13 @@
         <v>6</v>
       </c>
       <c r="B152" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C152">
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E152">
         <v>0.4379</v>
@@ -4042,13 +4006,13 @@
         <v>6</v>
       </c>
       <c r="B153" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C153">
         <v>10</v>
       </c>
       <c r="D153" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="E153">
         <v>0.5532</v>
@@ -4062,13 +4026,13 @@
         <v>6</v>
       </c>
       <c r="B154" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C154">
         <v>11</v>
       </c>
       <c r="D154" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E154">
         <v>0.3674</v>
@@ -4082,13 +4046,13 @@
         <v>16</v>
       </c>
       <c r="B155" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="D155" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E155">
         <v>0.5351</v>
@@ -4102,13 +4066,13 @@
         <v>16</v>
       </c>
       <c r="B156" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C156">
         <v>2</v>
       </c>
       <c r="D156" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E156">
         <v>0.5658</v>
@@ -4122,13 +4086,13 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C157">
         <v>3</v>
       </c>
       <c r="D157" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E157">
         <v>0.8372000000000001</v>
@@ -4142,13 +4106,13 @@
         <v>16</v>
       </c>
       <c r="B158" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C158">
         <v>4</v>
       </c>
       <c r="D158" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E158">
         <v>0.6856</v>
@@ -4162,13 +4126,13 @@
         <v>16</v>
       </c>
       <c r="B159" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C159">
         <v>5</v>
       </c>
       <c r="D159" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E159">
         <v>0.4722</v>
@@ -4182,13 +4146,13 @@
         <v>17</v>
       </c>
       <c r="B160" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E160">
         <v>0.5958</v>
@@ -4202,13 +4166,13 @@
         <v>17</v>
       </c>
       <c r="B161" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C161">
         <v>2</v>
       </c>
       <c r="D161" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E161">
         <v>0.5648</v>
@@ -4222,13 +4186,13 @@
         <v>17</v>
       </c>
       <c r="B162" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C162">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E162">
         <v>0.8122</v>
@@ -4242,13 +4206,13 @@
         <v>17</v>
       </c>
       <c r="B163" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C163">
         <v>4</v>
       </c>
       <c r="D163" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E163">
         <v>0.5341</v>
@@ -4262,13 +4226,13 @@
         <v>17</v>
       </c>
       <c r="B164" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C164">
         <v>5</v>
       </c>
       <c r="D164" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E164">
         <v>0.4946</v>
@@ -4282,13 +4246,13 @@
         <v>18</v>
       </c>
       <c r="B165" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E165">
         <v>0.45</v>
@@ -4302,13 +4266,13 @@
         <v>18</v>
       </c>
       <c r="B166" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C166">
         <v>2</v>
       </c>
       <c r="D166" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E166">
         <v>0.4242</v>
@@ -4322,13 +4286,13 @@
         <v>18</v>
       </c>
       <c r="B167" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C167">
         <v>3</v>
       </c>
       <c r="D167" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E167">
         <v>0.6752</v>
@@ -4342,13 +4306,13 @@
         <v>18</v>
       </c>
       <c r="B168" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C168">
         <v>4</v>
       </c>
       <c r="D168" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E168">
         <v>0.4821</v>
@@ -4362,13 +4326,13 @@
         <v>18</v>
       </c>
       <c r="B169" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C169">
         <v>5</v>
       </c>
       <c r="D169" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E169">
         <v>0.4399</v>
@@ -4382,13 +4346,13 @@
         <v>19</v>
       </c>
       <c r="B170" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E170">
         <v>0.5006</v>
@@ -4402,13 +4366,13 @@
         <v>19</v>
       </c>
       <c r="B171" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C171">
         <v>2</v>
       </c>
       <c r="D171" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E171">
         <v>0.5268</v>
@@ -4422,13 +4386,13 @@
         <v>19</v>
       </c>
       <c r="B172" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C172">
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E172">
         <v>0.8122</v>
@@ -4442,13 +4406,13 @@
         <v>19</v>
       </c>
       <c r="B173" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C173">
         <v>4</v>
       </c>
       <c r="D173" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E173">
         <v>0.5647</v>
@@ -4462,13 +4426,13 @@
         <v>19</v>
       </c>
       <c r="B174" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C174">
         <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E174">
         <v>0.4946</v>
@@ -4482,13 +4446,13 @@
         <v>20</v>
       </c>
       <c r="B175" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="E175">
         <v>0.4608</v>
@@ -4502,13 +4466,13 @@
         <v>20</v>
       </c>
       <c r="B176" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C176">
         <v>2</v>
       </c>
       <c r="D176" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E176">
         <v>0.6103</v>
@@ -4522,13 +4486,13 @@
         <v>20</v>
       </c>
       <c r="B177" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C177">
         <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E177">
         <v>0.6756</v>
@@ -4542,13 +4506,13 @@
         <v>20</v>
       </c>
       <c r="B178" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C178">
         <v>4</v>
       </c>
       <c r="D178" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="E178">
         <v>0.5163</v>
@@ -4562,13 +4526,13 @@
         <v>20</v>
       </c>
       <c r="B179" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C179">
         <v>5</v>
       </c>
       <c r="D179" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="E179">
         <v>0.4055</v>
@@ -4582,13 +4546,13 @@
         <v>21</v>
       </c>
       <c r="B180" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E180">
         <v>0.0973</v>
@@ -4602,13 +4566,13 @@
         <v>21</v>
       </c>
       <c r="B181" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C181">
         <v>2</v>
       </c>
       <c r="D181" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E181">
         <v>0.1698</v>
@@ -4622,13 +4586,13 @@
         <v>21</v>
       </c>
       <c r="B182" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C182">
         <v>3</v>
       </c>
       <c r="D182" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E182">
         <v>0.1855</v>
@@ -4642,13 +4606,13 @@
         <v>21</v>
       </c>
       <c r="B183" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C183">
         <v>4</v>
       </c>
       <c r="D183" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E183">
         <v>0.2859</v>
@@ -4662,13 +4626,13 @@
         <v>21</v>
       </c>
       <c r="B184" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C184">
         <v>5</v>
       </c>
       <c r="D184" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E184">
         <v>0.3047</v>
@@ -4682,13 +4646,13 @@
         <v>21</v>
       </c>
       <c r="B185" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C185">
         <v>6</v>
       </c>
       <c r="D185" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E185">
         <v>0.1898</v>
@@ -4702,13 +4666,13 @@
         <v>21</v>
       </c>
       <c r="B186" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C186">
         <v>7</v>
       </c>
       <c r="D186" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E186">
         <v>0.1813</v>
@@ -4722,13 +4686,13 @@
         <v>21</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C187">
         <v>8</v>
       </c>
       <c r="D187" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E187">
         <v>0.082</v>
@@ -4742,13 +4706,13 @@
         <v>21</v>
       </c>
       <c r="B188" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C188">
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E188">
         <v>0.2175</v>
@@ -4762,13 +4726,13 @@
         <v>21</v>
       </c>
       <c r="B189" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C189">
         <v>10</v>
       </c>
       <c r="D189" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E189">
         <v>0.2137</v>
@@ -4782,13 +4746,13 @@
         <v>21</v>
       </c>
       <c r="B190" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C190">
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E190">
         <v>0.2007</v>
@@ -4802,13 +4766,13 @@
         <v>21</v>
       </c>
       <c r="B191" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C191">
         <v>12</v>
       </c>
       <c r="D191" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E191">
         <v>0.1036</v>
@@ -4822,13 +4786,13 @@
         <v>21</v>
       </c>
       <c r="B192" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C192">
         <v>13</v>
       </c>
       <c r="D192" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E192">
         <v>0.2143</v>
@@ -4842,13 +4806,13 @@
         <v>21</v>
       </c>
       <c r="B193" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C193">
         <v>14</v>
       </c>
       <c r="D193" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E193">
         <v>0.1146</v>
@@ -4862,13 +4826,13 @@
         <v>21</v>
       </c>
       <c r="B194" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C194">
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E194">
         <v>0.1555</v>
@@ -4882,13 +4846,13 @@
         <v>21</v>
       </c>
       <c r="B195" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C195">
         <v>16</v>
       </c>
       <c r="D195" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E195">
         <v>0.3266</v>
@@ -4902,13 +4866,13 @@
         <v>21</v>
       </c>
       <c r="B196" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C196">
         <v>17</v>
       </c>
       <c r="D196" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E196">
         <v>0.2117</v>
@@ -4922,13 +4886,13 @@
         <v>21</v>
       </c>
       <c r="B197" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C197">
         <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E197">
         <v>0.3606</v>
@@ -4942,13 +4906,13 @@
         <v>21</v>
       </c>
       <c r="B198" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C198">
         <v>19</v>
       </c>
       <c r="D198" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E198">
         <v>0.2731</v>
@@ -4962,13 +4926,13 @@
         <v>21</v>
       </c>
       <c r="B199" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C199">
         <v>20</v>
       </c>
       <c r="D199" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E199">
         <v>0.298</v>
@@ -4982,13 +4946,13 @@
         <v>21</v>
       </c>
       <c r="B200" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C200">
         <v>21</v>
       </c>
       <c r="D200" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E200">
         <v>0.2657</v>
@@ -5002,13 +4966,13 @@
         <v>21</v>
       </c>
       <c r="B201" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C201">
         <v>22</v>
       </c>
       <c r="D201" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E201">
         <v>0.2808</v>
@@ -5022,13 +4986,13 @@
         <v>21</v>
       </c>
       <c r="B202" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C202">
         <v>23</v>
       </c>
       <c r="D202" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E202">
         <v>0.2233</v>
@@ -5042,13 +5006,13 @@
         <v>21</v>
       </c>
       <c r="B203" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C203">
         <v>24</v>
       </c>
       <c r="D203" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E203">
         <v>0.1682</v>
@@ -5062,13 +5026,13 @@
         <v>22</v>
       </c>
       <c r="B204" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="E204">
         <v>0.18</v>
@@ -5082,13 +5046,13 @@
         <v>22</v>
       </c>
       <c r="B205" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C205">
         <v>2</v>
       </c>
       <c r="D205" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E205">
         <v>0.1933</v>
@@ -5102,13 +5066,13 @@
         <v>22</v>
       </c>
       <c r="B206" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C206">
         <v>3</v>
       </c>
       <c r="D206" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="E206">
         <v>0.1658</v>
@@ -5122,13 +5086,13 @@
         <v>22</v>
       </c>
       <c r="B207" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C207">
         <v>4</v>
       </c>
       <c r="D207" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="E207">
         <v>0.2125</v>
@@ -5142,13 +5106,13 @@
         <v>22</v>
       </c>
       <c r="B208" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C208">
         <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="E208">
         <v>0.3514</v>
@@ -5162,13 +5126,13 @@
         <v>22</v>
       </c>
       <c r="B209" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C209">
         <v>6</v>
       </c>
       <c r="D209" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="E209">
         <v>0.2825</v>
@@ -5182,13 +5146,13 @@
         <v>22</v>
       </c>
       <c r="B210" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C210">
         <v>7</v>
       </c>
       <c r="D210" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="E210">
         <v>0.2293</v>
@@ -5202,13 +5166,13 @@
         <v>22</v>
       </c>
       <c r="B211" t="s">
-        <v>41</v>
-      </c>
-      <c r="C211" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="C211">
+        <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E211">
         <v>0.1449</v>
@@ -5222,13 +5186,13 @@
         <v>22</v>
       </c>
       <c r="B212" t="s">
-        <v>41</v>
-      </c>
-      <c r="C212" t="s">
-        <v>44</v>
+        <v>46</v>
+      </c>
+      <c r="C212">
+        <v>2</v>
       </c>
       <c r="D212" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E212">
         <v>0.1865</v>
@@ -5242,13 +5206,13 @@
         <v>22</v>
       </c>
       <c r="B213" t="s">
-        <v>41</v>
-      </c>
-      <c r="C213" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="C213">
+        <v>3</v>
       </c>
       <c r="D213" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E213">
         <v>0.2748</v>
@@ -5262,13 +5226,13 @@
         <v>22</v>
       </c>
       <c r="B214" t="s">
-        <v>41</v>
-      </c>
-      <c r="C214" t="s">
-        <v>46</v>
+        <v>46</v>
+      </c>
+      <c r="C214">
+        <v>4</v>
       </c>
       <c r="D214" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E214">
         <v>0.3114</v>
@@ -5282,13 +5246,13 @@
         <v>22</v>
       </c>
       <c r="B215" t="s">
-        <v>41</v>
-      </c>
-      <c r="C215" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="C215">
+        <v>5</v>
       </c>
       <c r="D215" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E215">
         <v>0.3704</v>
@@ -5302,13 +5266,13 @@
         <v>22</v>
       </c>
       <c r="B216" t="s">
-        <v>41</v>
-      </c>
-      <c r="C216" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="C216">
+        <v>6</v>
       </c>
       <c r="D216" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E216">
         <v>0.2685</v>
@@ -5322,13 +5286,13 @@
         <v>22</v>
       </c>
       <c r="B217" t="s">
-        <v>41</v>
-      </c>
-      <c r="C217" t="s">
-        <v>49</v>
+        <v>46</v>
+      </c>
+      <c r="C217">
+        <v>7</v>
       </c>
       <c r="D217" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E217">
         <v>0.1876</v>
@@ -5342,13 +5306,13 @@
         <v>22</v>
       </c>
       <c r="B218" t="s">
-        <v>41</v>
-      </c>
-      <c r="C218" t="s">
-        <v>50</v>
+        <v>46</v>
+      </c>
+      <c r="C218">
+        <v>8</v>
       </c>
       <c r="D218" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E218">
         <v>0.1371</v>
@@ -5362,13 +5326,13 @@
         <v>22</v>
       </c>
       <c r="B219" t="s">
-        <v>41</v>
-      </c>
-      <c r="C219" t="s">
-        <v>51</v>
+        <v>46</v>
+      </c>
+      <c r="C219">
+        <v>9</v>
       </c>
       <c r="D219" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E219">
         <v>0.2504</v>
@@ -5382,13 +5346,13 @@
         <v>22</v>
       </c>
       <c r="B220" t="s">
-        <v>41</v>
-      </c>
-      <c r="C220" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="C220">
+        <v>10</v>
       </c>
       <c r="D220" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E220">
         <v>0.2874</v>
@@ -5402,13 +5366,13 @@
         <v>22</v>
       </c>
       <c r="B221" t="s">
-        <v>41</v>
-      </c>
-      <c r="C221" t="s">
-        <v>53</v>
+        <v>46</v>
+      </c>
+      <c r="C221">
+        <v>11</v>
       </c>
       <c r="D221" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E221">
         <v>0.2726</v>
@@ -5422,13 +5386,13 @@
         <v>22</v>
       </c>
       <c r="B222" t="s">
-        <v>41</v>
-      </c>
-      <c r="C222" t="s">
-        <v>54</v>
+        <v>46</v>
+      </c>
+      <c r="C222">
+        <v>12</v>
       </c>
       <c r="D222" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E222">
         <v>0.1568</v>
@@ -5442,13 +5406,13 @@
         <v>22</v>
       </c>
       <c r="B223" t="s">
-        <v>41</v>
-      </c>
-      <c r="C223" t="s">
-        <v>55</v>
+        <v>46</v>
+      </c>
+      <c r="C223">
+        <v>13</v>
       </c>
       <c r="D223" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="E223">
         <v>0.2373</v>
@@ -5462,13 +5426,13 @@
         <v>22</v>
       </c>
       <c r="B224" t="s">
-        <v>41</v>
-      </c>
-      <c r="C224" t="s">
-        <v>56</v>
+        <v>46</v>
+      </c>
+      <c r="C224">
+        <v>14</v>
       </c>
       <c r="D224" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="E224">
         <v>0.2109</v>
@@ -5482,13 +5446,13 @@
         <v>22</v>
       </c>
       <c r="B225" t="s">
-        <v>41</v>
-      </c>
-      <c r="C225" t="s">
-        <v>57</v>
+        <v>46</v>
+      </c>
+      <c r="C225">
+        <v>15</v>
       </c>
       <c r="D225" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="E225">
         <v>0.2147</v>
@@ -5502,13 +5466,13 @@
         <v>22</v>
       </c>
       <c r="B226" t="s">
-        <v>41</v>
-      </c>
-      <c r="C226" t="s">
-        <v>58</v>
+        <v>46</v>
+      </c>
+      <c r="C226">
+        <v>16</v>
       </c>
       <c r="D226" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="E226">
         <v>0.3517</v>
@@ -5522,13 +5486,13 @@
         <v>22</v>
       </c>
       <c r="B227" t="s">
-        <v>41</v>
-      </c>
-      <c r="C227" t="s">
-        <v>59</v>
+        <v>46</v>
+      </c>
+      <c r="C227">
+        <v>17</v>
       </c>
       <c r="D227" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="E227">
         <v>0.2691</v>
@@ -5542,13 +5506,13 @@
         <v>22</v>
       </c>
       <c r="B228" t="s">
-        <v>41</v>
-      </c>
-      <c r="C228" t="s">
-        <v>60</v>
+        <v>46</v>
+      </c>
+      <c r="C228">
+        <v>18</v>
       </c>
       <c r="D228" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E228">
         <v>0.4198</v>
@@ -5562,13 +5526,13 @@
         <v>22</v>
       </c>
       <c r="B229" t="s">
-        <v>41</v>
-      </c>
-      <c r="C229" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="C229">
+        <v>19</v>
       </c>
       <c r="D229" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E229">
         <v>0.3182</v>
@@ -5582,13 +5546,13 @@
         <v>22</v>
       </c>
       <c r="B230" t="s">
-        <v>41</v>
-      </c>
-      <c r="C230" t="s">
-        <v>62</v>
+        <v>46</v>
+      </c>
+      <c r="C230">
+        <v>20</v>
       </c>
       <c r="D230" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="E230">
         <v>0.4125</v>
@@ -5602,13 +5566,13 @@
         <v>22</v>
       </c>
       <c r="B231" t="s">
-        <v>41</v>
-      </c>
-      <c r="C231" t="s">
-        <v>63</v>
+        <v>46</v>
+      </c>
+      <c r="C231">
+        <v>21</v>
       </c>
       <c r="D231" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="E231">
         <v>0.3677</v>
@@ -5622,13 +5586,13 @@
         <v>22</v>
       </c>
       <c r="B232" t="s">
-        <v>41</v>
-      </c>
-      <c r="C232" t="s">
-        <v>64</v>
+        <v>46</v>
+      </c>
+      <c r="C232">
+        <v>22</v>
       </c>
       <c r="D232" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E232">
         <v>0.3396</v>
@@ -5642,13 +5606,13 @@
         <v>22</v>
       </c>
       <c r="B233" t="s">
-        <v>41</v>
-      </c>
-      <c r="C233" t="s">
-        <v>65</v>
+        <v>46</v>
+      </c>
+      <c r="C233">
+        <v>23</v>
       </c>
       <c r="D233" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E233">
         <v>0.2825</v>
@@ -5662,18 +5626,1178 @@
         <v>22</v>
       </c>
       <c r="B234" t="s">
-        <v>41</v>
-      </c>
-      <c r="C234" t="s">
-        <v>66</v>
+        <v>46</v>
+      </c>
+      <c r="C234">
+        <v>24</v>
       </c>
       <c r="D234" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="E234">
         <v>0.2293</v>
       </c>
       <c r="F234" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
+      <c r="A235" t="s">
+        <v>23</v>
+      </c>
+      <c r="B235" t="s">
+        <v>44</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+      <c r="D235" t="s">
+        <v>142</v>
+      </c>
+      <c r="E235">
+        <v>0.5464</v>
+      </c>
+      <c r="F235" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
+      <c r="A236" t="s">
+        <v>23</v>
+      </c>
+      <c r="B236" t="s">
+        <v>44</v>
+      </c>
+      <c r="C236">
+        <v>2</v>
+      </c>
+      <c r="D236" t="s">
+        <v>143</v>
+      </c>
+      <c r="E236">
+        <v>0.7364000000000001</v>
+      </c>
+      <c r="F236" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
+      <c r="A237" t="s">
+        <v>23</v>
+      </c>
+      <c r="B237" t="s">
+        <v>44</v>
+      </c>
+      <c r="C237">
+        <v>3</v>
+      </c>
+      <c r="D237" t="s">
+        <v>144</v>
+      </c>
+      <c r="E237">
+        <v>0.8554</v>
+      </c>
+      <c r="F237" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
+      <c r="A238" t="s">
+        <v>23</v>
+      </c>
+      <c r="B238" t="s">
+        <v>44</v>
+      </c>
+      <c r="C238">
+        <v>4</v>
+      </c>
+      <c r="D238" t="s">
+        <v>145</v>
+      </c>
+      <c r="E238">
+        <v>0.6437</v>
+      </c>
+      <c r="F238" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
+      <c r="A239" t="s">
+        <v>23</v>
+      </c>
+      <c r="B239" t="s">
+        <v>44</v>
+      </c>
+      <c r="C239">
+        <v>5</v>
+      </c>
+      <c r="D239" t="s">
+        <v>146</v>
+      </c>
+      <c r="E239">
+        <v>0.6898</v>
+      </c>
+      <c r="F239" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
+      <c r="A240" t="s">
+        <v>24</v>
+      </c>
+      <c r="B240" t="s">
+        <v>44</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+      <c r="D240" t="s">
+        <v>142</v>
+      </c>
+      <c r="E240">
+        <v>0.6185</v>
+      </c>
+      <c r="F240" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241" t="s">
+        <v>24</v>
+      </c>
+      <c r="B241" t="s">
+        <v>44</v>
+      </c>
+      <c r="C241">
+        <v>2</v>
+      </c>
+      <c r="D241" t="s">
+        <v>143</v>
+      </c>
+      <c r="E241">
+        <v>0.735</v>
+      </c>
+      <c r="F241" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
+      <c r="A242" t="s">
+        <v>24</v>
+      </c>
+      <c r="B242" t="s">
+        <v>44</v>
+      </c>
+      <c r="C242">
+        <v>3</v>
+      </c>
+      <c r="D242" t="s">
+        <v>144</v>
+      </c>
+      <c r="E242">
+        <v>0.762</v>
+      </c>
+      <c r="F242" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
+      <c r="A243" t="s">
+        <v>24</v>
+      </c>
+      <c r="B243" t="s">
+        <v>44</v>
+      </c>
+      <c r="C243">
+        <v>4</v>
+      </c>
+      <c r="D243" t="s">
+        <v>145</v>
+      </c>
+      <c r="E243">
+        <v>0.6322</v>
+      </c>
+      <c r="F243" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
+      <c r="A244" t="s">
+        <v>24</v>
+      </c>
+      <c r="B244" t="s">
+        <v>44</v>
+      </c>
+      <c r="C244">
+        <v>5</v>
+      </c>
+      <c r="D244" t="s">
+        <v>146</v>
+      </c>
+      <c r="E244">
+        <v>0.6212</v>
+      </c>
+      <c r="F244" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
+      <c r="A245" t="s">
+        <v>25</v>
+      </c>
+      <c r="B245" t="s">
+        <v>44</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+      <c r="D245" t="s">
+        <v>142</v>
+      </c>
+      <c r="E245">
+        <v>0.5467</v>
+      </c>
+      <c r="F245" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
+      <c r="A246" t="s">
+        <v>25</v>
+      </c>
+      <c r="B246" t="s">
+        <v>44</v>
+      </c>
+      <c r="C246">
+        <v>2</v>
+      </c>
+      <c r="D246" t="s">
+        <v>143</v>
+      </c>
+      <c r="E246">
+        <v>0.7503</v>
+      </c>
+      <c r="F246" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
+      <c r="A247" t="s">
+        <v>25</v>
+      </c>
+      <c r="B247" t="s">
+        <v>44</v>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247" t="s">
+        <v>144</v>
+      </c>
+      <c r="E247">
+        <v>0.711</v>
+      </c>
+      <c r="F247" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
+      <c r="A248" t="s">
+        <v>25</v>
+      </c>
+      <c r="B248" t="s">
+        <v>44</v>
+      </c>
+      <c r="C248">
+        <v>4</v>
+      </c>
+      <c r="D248" t="s">
+        <v>145</v>
+      </c>
+      <c r="E248">
+        <v>0.5966</v>
+      </c>
+      <c r="F248" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
+      <c r="A249" t="s">
+        <v>25</v>
+      </c>
+      <c r="B249" t="s">
+        <v>44</v>
+      </c>
+      <c r="C249">
+        <v>5</v>
+      </c>
+      <c r="D249" t="s">
+        <v>146</v>
+      </c>
+      <c r="E249">
+        <v>0.613</v>
+      </c>
+      <c r="F249" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
+      <c r="A250" t="s">
+        <v>26</v>
+      </c>
+      <c r="B250" t="s">
+        <v>44</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+      <c r="D250" t="s">
+        <v>142</v>
+      </c>
+      <c r="E250">
+        <v>0.5165</v>
+      </c>
+      <c r="F250" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
+      <c r="A251" t="s">
+        <v>26</v>
+      </c>
+      <c r="B251" t="s">
+        <v>44</v>
+      </c>
+      <c r="C251">
+        <v>2</v>
+      </c>
+      <c r="D251" t="s">
+        <v>143</v>
+      </c>
+      <c r="E251">
+        <v>0.7318</v>
+      </c>
+      <c r="F251" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
+      <c r="A252" t="s">
+        <v>26</v>
+      </c>
+      <c r="B252" t="s">
+        <v>44</v>
+      </c>
+      <c r="C252">
+        <v>3</v>
+      </c>
+      <c r="D252" t="s">
+        <v>144</v>
+      </c>
+      <c r="E252">
+        <v>0.6741</v>
+      </c>
+      <c r="F252" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
+      <c r="A253" t="s">
+        <v>26</v>
+      </c>
+      <c r="B253" t="s">
+        <v>44</v>
+      </c>
+      <c r="C253">
+        <v>4</v>
+      </c>
+      <c r="D253" t="s">
+        <v>145</v>
+      </c>
+      <c r="E253">
+        <v>0.6514</v>
+      </c>
+      <c r="F253" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
+      <c r="A254" t="s">
+        <v>26</v>
+      </c>
+      <c r="B254" t="s">
+        <v>44</v>
+      </c>
+      <c r="C254">
+        <v>5</v>
+      </c>
+      <c r="D254" t="s">
+        <v>146</v>
+      </c>
+      <c r="E254">
+        <v>0.5609</v>
+      </c>
+      <c r="F254" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
+      <c r="A255" t="s">
+        <v>21</v>
+      </c>
+      <c r="B255" t="s">
+        <v>47</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+      <c r="D255" t="s">
+        <v>182</v>
+      </c>
+      <c r="E255">
+        <v>0.161</v>
+      </c>
+      <c r="F255" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
+      <c r="A256" t="s">
+        <v>21</v>
+      </c>
+      <c r="B256" t="s">
+        <v>47</v>
+      </c>
+      <c r="C256">
+        <v>2</v>
+      </c>
+      <c r="D256" t="s">
+        <v>183</v>
+      </c>
+      <c r="E256">
+        <v>0.1825</v>
+      </c>
+      <c r="F256" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
+      <c r="A257" t="s">
+        <v>21</v>
+      </c>
+      <c r="B257" t="s">
+        <v>47</v>
+      </c>
+      <c r="C257">
+        <v>3</v>
+      </c>
+      <c r="D257" t="s">
+        <v>184</v>
+      </c>
+      <c r="E257">
+        <v>0.1141</v>
+      </c>
+      <c r="F257" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
+      <c r="A258" t="s">
+        <v>21</v>
+      </c>
+      <c r="B258" t="s">
+        <v>47</v>
+      </c>
+      <c r="C258">
+        <v>4</v>
+      </c>
+      <c r="D258" t="s">
+        <v>185</v>
+      </c>
+      <c r="E258">
+        <v>0.1894</v>
+      </c>
+      <c r="F258" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
+      <c r="A259" t="s">
+        <v>21</v>
+      </c>
+      <c r="B259" t="s">
+        <v>47</v>
+      </c>
+      <c r="C259">
+        <v>5</v>
+      </c>
+      <c r="D259" t="s">
+        <v>186</v>
+      </c>
+      <c r="E259">
+        <v>0.2799</v>
+      </c>
+      <c r="F259" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
+      <c r="A260" t="s">
+        <v>21</v>
+      </c>
+      <c r="B260" t="s">
+        <v>47</v>
+      </c>
+      <c r="C260">
+        <v>6</v>
+      </c>
+      <c r="D260" t="s">
+        <v>187</v>
+      </c>
+      <c r="E260">
+        <v>0.2233</v>
+      </c>
+      <c r="F260" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
+      <c r="A261" t="s">
+        <v>21</v>
+      </c>
+      <c r="B261" t="s">
+        <v>47</v>
+      </c>
+      <c r="C261">
+        <v>7</v>
+      </c>
+      <c r="D261" t="s">
+        <v>188</v>
+      </c>
+      <c r="E261">
+        <v>0.1682</v>
+      </c>
+      <c r="F261" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>27</v>
+      </c>
+      <c r="B262" t="s">
+        <v>46</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+      <c r="D262" t="s">
+        <v>158</v>
+      </c>
+      <c r="E262">
+        <v>0.1011</v>
+      </c>
+      <c r="F262" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>27</v>
+      </c>
+      <c r="B263" t="s">
+        <v>46</v>
+      </c>
+      <c r="C263">
+        <v>2</v>
+      </c>
+      <c r="D263" t="s">
+        <v>159</v>
+      </c>
+      <c r="E263">
+        <v>0.1632</v>
+      </c>
+      <c r="F263" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>27</v>
+      </c>
+      <c r="B264" t="s">
+        <v>46</v>
+      </c>
+      <c r="C264">
+        <v>3</v>
+      </c>
+      <c r="D264" t="s">
+        <v>160</v>
+      </c>
+      <c r="E264">
+        <v>0.1748</v>
+      </c>
+      <c r="F264" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>27</v>
+      </c>
+      <c r="B265" t="s">
+        <v>46</v>
+      </c>
+      <c r="C265">
+        <v>4</v>
+      </c>
+      <c r="D265" t="s">
+        <v>161</v>
+      </c>
+      <c r="E265">
+        <v>0.2735</v>
+      </c>
+      <c r="F265" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>27</v>
+      </c>
+      <c r="B266" t="s">
+        <v>46</v>
+      </c>
+      <c r="C266">
+        <v>5</v>
+      </c>
+      <c r="D266" t="s">
+        <v>162</v>
+      </c>
+      <c r="E266">
+        <v>0.2881</v>
+      </c>
+      <c r="F266" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>27</v>
+      </c>
+      <c r="B267" t="s">
+        <v>46</v>
+      </c>
+      <c r="C267">
+        <v>6</v>
+      </c>
+      <c r="D267" t="s">
+        <v>163</v>
+      </c>
+      <c r="E267">
+        <v>0.1715</v>
+      </c>
+      <c r="F267" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>27</v>
+      </c>
+      <c r="B268" t="s">
+        <v>46</v>
+      </c>
+      <c r="C268">
+        <v>7</v>
+      </c>
+      <c r="D268" t="s">
+        <v>164</v>
+      </c>
+      <c r="E268">
+        <v>0.1732</v>
+      </c>
+      <c r="F268" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>27</v>
+      </c>
+      <c r="B269" t="s">
+        <v>46</v>
+      </c>
+      <c r="C269">
+        <v>8</v>
+      </c>
+      <c r="D269" t="s">
+        <v>165</v>
+      </c>
+      <c r="E269">
+        <v>0.0798</v>
+      </c>
+      <c r="F269" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>27</v>
+      </c>
+      <c r="B270" t="s">
+        <v>46</v>
+      </c>
+      <c r="C270">
+        <v>9</v>
+      </c>
+      <c r="D270" t="s">
+        <v>166</v>
+      </c>
+      <c r="E270">
+        <v>0.1997</v>
+      </c>
+      <c r="F270" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>27</v>
+      </c>
+      <c r="B271" t="s">
+        <v>46</v>
+      </c>
+      <c r="C271">
+        <v>10</v>
+      </c>
+      <c r="D271" t="s">
+        <v>167</v>
+      </c>
+      <c r="E271">
+        <v>0.1894</v>
+      </c>
+      <c r="F271" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>27</v>
+      </c>
+      <c r="B272" t="s">
+        <v>46</v>
+      </c>
+      <c r="C272">
+        <v>11</v>
+      </c>
+      <c r="D272" t="s">
+        <v>168</v>
+      </c>
+      <c r="E272">
+        <v>0.1766</v>
+      </c>
+      <c r="F272" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>27</v>
+      </c>
+      <c r="B273" t="s">
+        <v>46</v>
+      </c>
+      <c r="C273">
+        <v>12</v>
+      </c>
+      <c r="D273" t="s">
+        <v>169</v>
+      </c>
+      <c r="E273">
+        <v>0.1057</v>
+      </c>
+      <c r="F273" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>27</v>
+      </c>
+      <c r="B274" t="s">
+        <v>46</v>
+      </c>
+      <c r="C274">
+        <v>13</v>
+      </c>
+      <c r="D274" t="s">
+        <v>170</v>
+      </c>
+      <c r="E274">
+        <v>0.1861</v>
+      </c>
+      <c r="F274" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>27</v>
+      </c>
+      <c r="B275" t="s">
+        <v>46</v>
+      </c>
+      <c r="C275">
+        <v>14</v>
+      </c>
+      <c r="D275" t="s">
+        <v>171</v>
+      </c>
+      <c r="E275">
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="F275" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>27</v>
+      </c>
+      <c r="B276" t="s">
+        <v>46</v>
+      </c>
+      <c r="C276">
+        <v>15</v>
+      </c>
+      <c r="D276" t="s">
+        <v>172</v>
+      </c>
+      <c r="E276">
+        <v>0.1424</v>
+      </c>
+      <c r="F276" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>27</v>
+      </c>
+      <c r="B277" t="s">
+        <v>46</v>
+      </c>
+      <c r="C277">
+        <v>16</v>
+      </c>
+      <c r="D277" t="s">
+        <v>173</v>
+      </c>
+      <c r="E277">
+        <v>0.3207</v>
+      </c>
+      <c r="F277" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>27</v>
+      </c>
+      <c r="B278" t="s">
+        <v>46</v>
+      </c>
+      <c r="C278">
+        <v>17</v>
+      </c>
+      <c r="D278" t="s">
+        <v>174</v>
+      </c>
+      <c r="E278">
+        <v>0.1957</v>
+      </c>
+      <c r="F278" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>27</v>
+      </c>
+      <c r="B279" t="s">
+        <v>46</v>
+      </c>
+      <c r="C279">
+        <v>18</v>
+      </c>
+      <c r="D279" t="s">
+        <v>175</v>
+      </c>
+      <c r="E279">
+        <v>0.3507</v>
+      </c>
+      <c r="F279" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>27</v>
+      </c>
+      <c r="B280" t="s">
+        <v>46</v>
+      </c>
+      <c r="C280">
+        <v>19</v>
+      </c>
+      <c r="D280" t="s">
+        <v>176</v>
+      </c>
+      <c r="E280">
+        <v>0.2492</v>
+      </c>
+      <c r="F280" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>27</v>
+      </c>
+      <c r="B281" t="s">
+        <v>46</v>
+      </c>
+      <c r="C281">
+        <v>20</v>
+      </c>
+      <c r="D281" t="s">
+        <v>177</v>
+      </c>
+      <c r="E281">
+        <v>0.2699</v>
+      </c>
+      <c r="F281" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>27</v>
+      </c>
+      <c r="B282" t="s">
+        <v>46</v>
+      </c>
+      <c r="C282">
+        <v>21</v>
+      </c>
+      <c r="D282" t="s">
+        <v>178</v>
+      </c>
+      <c r="E282">
+        <v>0.2392</v>
+      </c>
+      <c r="F282" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>27</v>
+      </c>
+      <c r="B283" t="s">
+        <v>46</v>
+      </c>
+      <c r="C283">
+        <v>22</v>
+      </c>
+      <c r="D283" t="s">
+        <v>179</v>
+      </c>
+      <c r="E283">
+        <v>0.2686</v>
+      </c>
+      <c r="F283" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>27</v>
+      </c>
+      <c r="B284" t="s">
+        <v>46</v>
+      </c>
+      <c r="C284">
+        <v>23</v>
+      </c>
+      <c r="D284" t="s">
+        <v>180</v>
+      </c>
+      <c r="E284">
+        <v>0.2084</v>
+      </c>
+      <c r="F284" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>27</v>
+      </c>
+      <c r="B285" t="s">
+        <v>46</v>
+      </c>
+      <c r="C285">
+        <v>24</v>
+      </c>
+      <c r="D285" t="s">
+        <v>181</v>
+      </c>
+      <c r="E285">
+        <v>0.152</v>
+      </c>
+      <c r="F285" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>27</v>
+      </c>
+      <c r="B286" t="s">
+        <v>47</v>
+      </c>
+      <c r="C286" t="s">
+        <v>48</v>
+      </c>
+      <c r="D286" t="s">
+        <v>182</v>
+      </c>
+      <c r="E286">
+        <v>0.152</v>
+      </c>
+      <c r="F286" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>27</v>
+      </c>
+      <c r="B287" t="s">
+        <v>47</v>
+      </c>
+      <c r="C287" t="s">
+        <v>49</v>
+      </c>
+      <c r="D287" t="s">
+        <v>183</v>
+      </c>
+      <c r="E287">
+        <v>0.1738</v>
+      </c>
+      <c r="F287" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>27</v>
+      </c>
+      <c r="B288" t="s">
+        <v>47</v>
+      </c>
+      <c r="C288" t="s">
+        <v>50</v>
+      </c>
+      <c r="D288" t="s">
+        <v>184</v>
+      </c>
+      <c r="E288">
+        <v>0.0951</v>
+      </c>
+      <c r="F288" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>27</v>
+      </c>
+      <c r="B289" t="s">
+        <v>47</v>
+      </c>
+      <c r="C289" t="s">
+        <v>51</v>
+      </c>
+      <c r="D289" t="s">
+        <v>185</v>
+      </c>
+      <c r="E289">
+        <v>0.1658</v>
+      </c>
+      <c r="F289" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>27</v>
+      </c>
+      <c r="B290" t="s">
+        <v>47</v>
+      </c>
+      <c r="C290" t="s">
+        <v>52</v>
+      </c>
+      <c r="D290" t="s">
+        <v>186</v>
+      </c>
+      <c r="E290">
+        <v>0.2616</v>
+      </c>
+      <c r="F290" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>27</v>
+      </c>
+      <c r="B291" t="s">
+        <v>47</v>
+      </c>
+      <c r="C291" t="s">
+        <v>53</v>
+      </c>
+      <c r="D291" t="s">
+        <v>187</v>
+      </c>
+      <c r="E291">
+        <v>0.2084</v>
+      </c>
+      <c r="F291" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>27</v>
+      </c>
+      <c r="B292" t="s">
+        <v>47</v>
+      </c>
+      <c r="C292" t="s">
+        <v>54</v>
+      </c>
+      <c r="D292" t="s">
+        <v>188</v>
+      </c>
+      <c r="E292">
+        <v>0.152</v>
+      </c>
+      <c r="F292" t="b">
         <v>0</v>
       </c>
     </row>
